--- a/AAII_Financials/Quarterly/BGI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BGI_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
   <si>
     <t>BGI</t>
   </si>
@@ -656,280 +656,293 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45192</v>
+      </c>
+      <c r="E7" s="2">
         <v>45010</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44828</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44646</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44464</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44282</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43918</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43736</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>43554</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>43372</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>43190</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43001</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>42819</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>42637</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>42455</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>42273</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>42091</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>41909</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>60300</v>
+        <v>64900</v>
       </c>
       <c r="E8" s="3">
-        <v>58200</v>
+        <v>61300</v>
       </c>
       <c r="F8" s="3">
-        <v>70300</v>
+        <v>59100</v>
       </c>
       <c r="G8" s="3">
-        <v>61500</v>
+        <v>71500</v>
       </c>
       <c r="H8" s="3">
         <v>62500</v>
       </c>
       <c r="I8" s="3">
-        <v>41400</v>
+        <v>63600</v>
       </c>
       <c r="J8" s="3">
+        <v>42100</v>
+      </c>
+      <c r="K8" s="3">
         <v>61100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>63200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>61800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>52700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>63500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>54000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>46900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>39900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>113000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>99700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>161900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>139700</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>35500</v>
+        <v>38200</v>
       </c>
       <c r="E9" s="3">
-        <v>33600</v>
+        <v>36100</v>
       </c>
       <c r="F9" s="3">
-        <v>40300</v>
+        <v>34100</v>
       </c>
       <c r="G9" s="3">
-        <v>36200</v>
+        <v>40900</v>
       </c>
       <c r="H9" s="3">
-        <v>38200</v>
+        <v>36800</v>
       </c>
       <c r="I9" s="3">
-        <v>24900</v>
+        <v>38800</v>
       </c>
       <c r="J9" s="3">
+        <v>25300</v>
+      </c>
+      <c r="K9" s="3">
         <v>38000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>39100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>37600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>32500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>40500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>32300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>28400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>23500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>70000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>61300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>99500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>84300</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>24800</v>
+        <v>26600</v>
       </c>
       <c r="E10" s="3">
-        <v>24600</v>
+        <v>25200</v>
       </c>
       <c r="F10" s="3">
-        <v>30000</v>
+        <v>25000</v>
       </c>
       <c r="G10" s="3">
-        <v>25400</v>
+        <v>30500</v>
       </c>
       <c r="H10" s="3">
-        <v>24300</v>
+        <v>25800</v>
       </c>
       <c r="I10" s="3">
-        <v>16600</v>
+        <v>24700</v>
       </c>
       <c r="J10" s="3">
+        <v>16900</v>
+      </c>
+      <c r="K10" s="3">
         <v>23200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>24100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>24200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>20200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>23100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>21600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>18500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>16400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>43000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>38400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>62400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>55400</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -951,8 +964,9 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1010,8 +1024,11 @@
       <c r="U12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1069,8 +1086,11 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1086,109 +1106,115 @@
       <c r="G14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J14" s="3">
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K14" s="3">
         <v>200</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2900</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>500</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>5500</v>
       </c>
-      <c r="U14" s="3" t="s">
+      <c r="V14" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2200</v>
+        <v>2300</v>
       </c>
       <c r="E15" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F15" s="3">
         <v>1900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1800</v>
       </c>
-      <c r="G15" s="3">
-        <v>2400</v>
-      </c>
       <c r="H15" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I15" s="3">
         <v>1900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2100</v>
-      </c>
-      <c r="J15" s="3">
-        <v>1800</v>
       </c>
       <c r="K15" s="3">
         <v>1800</v>
       </c>
       <c r="L15" s="3">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="M15" s="3">
         <v>1500</v>
       </c>
       <c r="N15" s="3">
+        <v>1500</v>
+      </c>
+      <c r="O15" s="3">
         <v>1300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>2000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>1900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>2900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1207,126 +1233,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>62600</v>
+      <c r="D17" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E17" s="3">
-        <v>58700</v>
+        <v>63600</v>
       </c>
       <c r="F17" s="3">
-        <v>69000</v>
+        <v>59600</v>
       </c>
       <c r="G17" s="3">
-        <v>59600</v>
+        <v>70200</v>
       </c>
       <c r="H17" s="3">
-        <v>63600</v>
+        <v>60600</v>
       </c>
       <c r="I17" s="3">
-        <v>42500</v>
+        <v>64600</v>
       </c>
       <c r="J17" s="3">
+        <v>43200</v>
+      </c>
+      <c r="K17" s="3">
         <v>64400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>64700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>65700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>59200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>73000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>58800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>48100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>41300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>106000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>95200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>161900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>137000</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1300</v>
       </c>
-      <c r="G18" s="3">
-        <v>1900</v>
-      </c>
       <c r="H18" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I18" s="3">
         <v>-1100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-3200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-3900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-6500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-9500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-4900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>7000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>4500</v>
       </c>
-      <c r="T18" s="3">
-        <v>0</v>
-      </c>
       <c r="U18" s="3">
+        <v>0</v>
+      </c>
+      <c r="V18" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1348,20 +1381,21 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E20" s="3">
+        <v>800</v>
+      </c>
+      <c r="F20" s="3">
         <v>700</v>
       </c>
-      <c r="E20" s="3">
-        <v>700</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
@@ -1407,185 +1441,197 @@
       <c r="U20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>700</v>
+      <c r="D21" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E21" s="3">
-        <v>2100</v>
+        <v>2600</v>
       </c>
       <c r="F21" s="3">
-        <v>3100</v>
+        <v>-2200</v>
       </c>
       <c r="G21" s="3">
-        <v>4400</v>
+        <v>5600</v>
       </c>
       <c r="H21" s="3">
-        <v>900</v>
+        <v>400</v>
       </c>
       <c r="I21" s="3">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="J21" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="K21" s="3">
         <v>-1500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-2400</v>
       </c>
-      <c r="M21" s="3" t="s">
+      <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-8200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-3500</v>
-      </c>
-      <c r="P21" s="3">
-        <v>-400</v>
       </c>
       <c r="Q21" s="3">
         <v>-400</v>
       </c>
       <c r="R21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="S21" s="3">
         <v>7200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>6400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E22" s="3">
         <v>2400</v>
       </c>
-      <c r="E22" s="3">
-        <v>1600</v>
-      </c>
       <c r="F22" s="3">
+        <v>1700</v>
+      </c>
+      <c r="G22" s="3">
         <v>1100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J22" s="3">
         <v>1100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
+        <v>2400</v>
+      </c>
+      <c r="L22" s="3">
+        <v>1800</v>
+      </c>
+      <c r="M22" s="3">
+        <v>2100</v>
+      </c>
+      <c r="N22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="O22" s="3">
+        <v>2000</v>
+      </c>
+      <c r="P22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Q22" s="3">
         <v>1000</v>
       </c>
-      <c r="J22" s="3">
-        <v>2400</v>
-      </c>
-      <c r="K22" s="3">
-        <v>1800</v>
-      </c>
-      <c r="L22" s="3">
-        <v>2100</v>
-      </c>
-      <c r="M22" s="3">
-        <v>1400</v>
-      </c>
-      <c r="N22" s="3">
-        <v>2000</v>
-      </c>
-      <c r="O22" s="3">
-        <v>1200</v>
-      </c>
-      <c r="P22" s="3">
-        <v>1000</v>
-      </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>3600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>3900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>4600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-4000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-5600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-3300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-6000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-7900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-11400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-6100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-4600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1643,8 +1689,11 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1702,126 +1751,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-5600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-3300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-6000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-11400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-6100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>3400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-4600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-5600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-6000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-7900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-11400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-6100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>3400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-4600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1879,8 +1937,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1896,50 +1957,53 @@
       <c r="G29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
+      <c r="H29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I29" s="3">
         <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>-300</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-100</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>-300</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>26700</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>1500</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>7600</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>1500</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
+      <c r="T29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1997,8 +2061,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2056,20 +2123,23 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F32" s="3">
         <v>-700</v>
       </c>
-      <c r="E32" s="3">
-        <v>-700</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
@@ -2115,67 +2185,73 @@
       <c r="U32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-6000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-8300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>15300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-4600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>5300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>3400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-4600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2233,131 +2309,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-6000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-8300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>15300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-4600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>5300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>3400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-4600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45192</v>
+      </c>
+      <c r="E38" s="2">
         <v>45010</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44828</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44646</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44464</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44282</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43918</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43736</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>43554</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>43372</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>43190</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43001</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>42819</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>42637</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>42455</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>42273</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>42091</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>41909</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2379,8 +2464,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2402,67 +2488,71 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E41" s="3">
         <v>900</v>
       </c>
-      <c r="E41" s="3">
-        <v>1100</v>
-      </c>
       <c r="F41" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G41" s="3">
         <v>1500</v>
       </c>
-      <c r="G41" s="3">
-        <v>1900</v>
-      </c>
       <c r="H41" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I41" s="3">
         <v>1300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1200</v>
-      </c>
-      <c r="L41" s="3">
-        <v>900</v>
       </c>
       <c r="M41" s="3">
         <v>900</v>
       </c>
       <c r="N41" s="3">
+        <v>900</v>
+      </c>
+      <c r="O41" s="3">
         <v>800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2520,126 +2610,135 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>8300</v>
+        <v>6700</v>
       </c>
       <c r="E43" s="3">
-        <v>8800</v>
+        <v>8400</v>
       </c>
       <c r="F43" s="3">
-        <v>5800</v>
+        <v>9000</v>
       </c>
       <c r="G43" s="3">
         <v>5900</v>
       </c>
       <c r="H43" s="3">
-        <v>5300</v>
+        <v>6000</v>
       </c>
       <c r="I43" s="3">
+        <v>5400</v>
+      </c>
+      <c r="J43" s="3">
         <v>4600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>10300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>7300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>7700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>6800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>7700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>64200</v>
+        <v>68000</v>
       </c>
       <c r="E44" s="3">
-        <v>56600</v>
+        <v>65300</v>
       </c>
       <c r="F44" s="3">
-        <v>57400</v>
+        <v>57600</v>
       </c>
       <c r="G44" s="3">
-        <v>64400</v>
+        <v>58300</v>
       </c>
       <c r="H44" s="3">
-        <v>71100</v>
+        <v>65400</v>
       </c>
       <c r="I44" s="3">
-        <v>72900</v>
+        <v>72300</v>
       </c>
       <c r="J44" s="3">
         <v>74100</v>
       </c>
       <c r="K44" s="3">
+        <v>74100</v>
+      </c>
+      <c r="L44" s="3">
         <v>75300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>68700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>67900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>66100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>59700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>100500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>103800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>102600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>101300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>135700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>150400</v>
       </c>
     </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2647,16 +2746,16 @@
         <v>2000</v>
       </c>
       <c r="E45" s="3">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="F45" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G45" s="3">
         <v>1300</v>
       </c>
-      <c r="G45" s="3">
-        <v>1500</v>
-      </c>
       <c r="H45" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="I45" s="3">
         <v>1500</v>
@@ -2668,134 +2767,140 @@
         <v>1500</v>
       </c>
       <c r="L45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="M45" s="3">
         <v>1600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>82200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>75400</v>
+        <v>78200</v>
       </c>
       <c r="E46" s="3">
-        <v>68500</v>
+        <v>76600</v>
       </c>
       <c r="F46" s="3">
-        <v>66000</v>
+        <v>69600</v>
       </c>
       <c r="G46" s="3">
-        <v>73800</v>
+        <v>67100</v>
       </c>
       <c r="H46" s="3">
-        <v>79200</v>
+        <v>75000</v>
       </c>
       <c r="I46" s="3">
-        <v>80700</v>
+        <v>80500</v>
       </c>
       <c r="J46" s="3">
+        <v>82100</v>
+      </c>
+      <c r="K46" s="3">
         <v>80300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>82500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>73900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>74500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>75600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>147700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>114000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>115600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>113300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>112500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>148000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>162600</v>
       </c>
     </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E47" s="3">
         <v>2900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
+        <v>3400</v>
+      </c>
+      <c r="G47" s="3">
+        <v>4100</v>
+      </c>
+      <c r="H47" s="3">
+        <v>4200</v>
+      </c>
+      <c r="I47" s="3">
+        <v>4200</v>
+      </c>
+      <c r="J47" s="3">
+        <v>3500</v>
+      </c>
+      <c r="K47" s="3">
         <v>3300</v>
       </c>
-      <c r="F47" s="3">
-        <v>4100</v>
-      </c>
-      <c r="G47" s="3">
-        <v>4200</v>
-      </c>
-      <c r="H47" s="3">
-        <v>4100</v>
-      </c>
-      <c r="I47" s="3">
-        <v>3400</v>
-      </c>
-      <c r="J47" s="3">
-        <v>3300</v>
-      </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>700</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>4</v>
+      <c r="O47" s="3">
+        <v>0</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>4</v>
@@ -2809,90 +2914,96 @@
       <c r="S47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T47" s="3">
-        <v>0</v>
+      <c r="T47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>59900</v>
+        <v>58400</v>
       </c>
       <c r="E48" s="3">
-        <v>59600</v>
+        <v>60800</v>
       </c>
       <c r="F48" s="3">
-        <v>58800</v>
+        <v>60600</v>
       </c>
       <c r="G48" s="3">
-        <v>59800</v>
+        <v>59700</v>
       </c>
       <c r="H48" s="3">
-        <v>59700</v>
+        <v>60700</v>
       </c>
       <c r="I48" s="3">
-        <v>62000</v>
+        <v>60700</v>
       </c>
       <c r="J48" s="3">
+        <v>63000</v>
+      </c>
+      <c r="K48" s="3">
         <v>65900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>68900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>22300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>18400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>15100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>11900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>17500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>21200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>21900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>22100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>28500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>31700</v>
       </c>
     </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>5100</v>
+        <v>5600</v>
       </c>
       <c r="E49" s="3">
-        <v>4300</v>
+        <v>5200</v>
       </c>
       <c r="F49" s="3">
         <v>4400</v>
       </c>
       <c r="G49" s="3">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="H49" s="3">
-        <v>3600</v>
+        <v>4100</v>
       </c>
       <c r="I49" s="3">
         <v>3600</v>
@@ -2901,40 +3012,43 @@
         <v>3600</v>
       </c>
       <c r="K49" s="3">
+        <v>3600</v>
+      </c>
+      <c r="L49" s="3">
         <v>3200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2800</v>
-      </c>
-      <c r="P49" s="3">
-        <v>500</v>
       </c>
       <c r="Q49" s="3">
         <v>500</v>
       </c>
       <c r="R49" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="S49" s="3">
         <v>600</v>
       </c>
       <c r="T49" s="3">
+        <v>600</v>
+      </c>
+      <c r="U49" s="3">
         <v>900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2992,8 +3106,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3051,8 +3168,11 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3093,25 +3213,28 @@
         <v>0</v>
       </c>
       <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3">
         <v>4200</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>400</v>
       </c>
       <c r="R52" s="3">
         <v>400</v>
       </c>
       <c r="S52" s="3">
+        <v>400</v>
+      </c>
+      <c r="T52" s="3">
         <v>1600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3169,67 +3292,73 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>143200</v>
+        <v>145800</v>
       </c>
       <c r="E54" s="3">
-        <v>135800</v>
+        <v>145600</v>
       </c>
       <c r="F54" s="3">
-        <v>133200</v>
+        <v>138000</v>
       </c>
       <c r="G54" s="3">
-        <v>141700</v>
+        <v>135400</v>
       </c>
       <c r="H54" s="3">
-        <v>146600</v>
+        <v>144000</v>
       </c>
       <c r="I54" s="3">
-        <v>149700</v>
+        <v>149000</v>
       </c>
       <c r="J54" s="3">
+        <v>152200</v>
+      </c>
+      <c r="K54" s="3">
         <v>153100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>157600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>100500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>98200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>93800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>162300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>136200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>137700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>136200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>136800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>180200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>198300</v>
       </c>
     </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3251,8 +3380,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3274,362 +3404,381 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>27400</v>
+        <v>28500</v>
       </c>
       <c r="E57" s="3">
-        <v>19500</v>
+        <v>27800</v>
       </c>
       <c r="F57" s="3">
+        <v>19900</v>
+      </c>
+      <c r="G57" s="3">
+        <v>20900</v>
+      </c>
+      <c r="H57" s="3">
+        <v>25600</v>
+      </c>
+      <c r="I57" s="3">
+        <v>28100</v>
+      </c>
+      <c r="J57" s="3">
+        <v>26700</v>
+      </c>
+      <c r="K57" s="3">
+        <v>35000</v>
+      </c>
+      <c r="L57" s="3">
+        <v>29700</v>
+      </c>
+      <c r="M57" s="3">
+        <v>25000</v>
+      </c>
+      <c r="N57" s="3">
+        <v>20800</v>
+      </c>
+      <c r="O57" s="3">
         <v>20600</v>
       </c>
-      <c r="G57" s="3">
-        <v>25200</v>
-      </c>
-      <c r="H57" s="3">
-        <v>27600</v>
-      </c>
-      <c r="I57" s="3">
-        <v>26300</v>
-      </c>
-      <c r="J57" s="3">
-        <v>35000</v>
-      </c>
-      <c r="K57" s="3">
-        <v>29700</v>
-      </c>
-      <c r="L57" s="3">
-        <v>25000</v>
-      </c>
-      <c r="M57" s="3">
-        <v>20800</v>
-      </c>
-      <c r="N57" s="3">
-        <v>20600</v>
-      </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>19000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>35500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>35100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>34800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>31800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>44700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>46000</v>
       </c>
     </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>43600</v>
+        <v>47200</v>
       </c>
       <c r="E58" s="3">
-        <v>39200</v>
+        <v>44400</v>
       </c>
       <c r="F58" s="3">
-        <v>32900</v>
+        <v>39800</v>
       </c>
       <c r="G58" s="3">
-        <v>37500</v>
+        <v>33500</v>
       </c>
       <c r="H58" s="3">
-        <v>41000</v>
+        <v>38100</v>
       </c>
       <c r="I58" s="3">
-        <v>45500</v>
+        <v>41600</v>
       </c>
       <c r="J58" s="3">
+        <v>46200</v>
+      </c>
+      <c r="K58" s="3">
         <v>42200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>44800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>36100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>36000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>31400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>46100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>55700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>56800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>50700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>58200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>69100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>79600</v>
       </c>
     </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>10500</v>
+        <v>9200</v>
       </c>
       <c r="E59" s="3">
-        <v>9900</v>
+        <v>10600</v>
       </c>
       <c r="F59" s="3">
-        <v>11100</v>
+        <v>10100</v>
       </c>
       <c r="G59" s="3">
-        <v>12600</v>
+        <v>11300</v>
       </c>
       <c r="H59" s="3">
-        <v>12700</v>
+        <v>12800</v>
       </c>
       <c r="I59" s="3">
-        <v>9400</v>
+        <v>12900</v>
       </c>
       <c r="J59" s="3">
+        <v>9500</v>
+      </c>
+      <c r="K59" s="3">
         <v>7600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>8900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>79300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>6400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>5600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>6700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>5700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>8100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>81500</v>
+        <v>84900</v>
       </c>
       <c r="E60" s="3">
-        <v>68600</v>
+        <v>82800</v>
       </c>
       <c r="F60" s="3">
-        <v>64600</v>
+        <v>69800</v>
       </c>
       <c r="G60" s="3">
-        <v>75300</v>
+        <v>65700</v>
       </c>
       <c r="H60" s="3">
-        <v>81300</v>
+        <v>76500</v>
       </c>
       <c r="I60" s="3">
-        <v>81100</v>
+        <v>82600</v>
       </c>
       <c r="J60" s="3">
+        <v>82500</v>
+      </c>
+      <c r="K60" s="3">
         <v>84900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>83500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>68300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>63400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>57800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>144500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>97600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>97500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>92200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>95700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>121900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>133400</v>
       </c>
     </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>16100</v>
+        <v>17100</v>
       </c>
       <c r="E61" s="3">
-        <v>16000</v>
+        <v>16400</v>
       </c>
       <c r="F61" s="3">
-        <v>15500</v>
+        <v>16300</v>
       </c>
       <c r="G61" s="3">
-        <v>16300</v>
+        <v>15800</v>
       </c>
       <c r="H61" s="3">
-        <v>16800</v>
+        <v>16500</v>
       </c>
       <c r="I61" s="3">
-        <v>17100</v>
+        <v>17000</v>
       </c>
       <c r="J61" s="3">
+        <v>17400</v>
+      </c>
+      <c r="K61" s="3">
         <v>11800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>10700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>12100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>11100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>23200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>32400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>34700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>36200</v>
-      </c>
-      <c r="T61" s="3">
-        <v>52000</v>
       </c>
       <c r="U61" s="3">
         <v>52000</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>52000</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>46100</v>
+        <v>45300</v>
       </c>
       <c r="E62" s="3">
-        <v>48000</v>
+        <v>46800</v>
       </c>
       <c r="F62" s="3">
         <v>48800</v>
       </c>
       <c r="G62" s="3">
-        <v>50500</v>
+        <v>49600</v>
       </c>
       <c r="H62" s="3">
-        <v>49600</v>
+        <v>51300</v>
       </c>
       <c r="I62" s="3">
-        <v>51000</v>
+        <v>50400</v>
       </c>
       <c r="J62" s="3">
+        <v>51900</v>
+      </c>
+      <c r="K62" s="3">
         <v>54000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>54700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>9700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3687,8 +3836,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3746,8 +3898,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3805,67 +3960,73 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>143600</v>
+        <v>147300</v>
       </c>
       <c r="E66" s="3">
-        <v>132600</v>
+        <v>146000</v>
       </c>
       <c r="F66" s="3">
-        <v>129000</v>
+        <v>134800</v>
       </c>
       <c r="G66" s="3">
-        <v>142000</v>
+        <v>131100</v>
       </c>
       <c r="H66" s="3">
-        <v>147700</v>
+        <v>144400</v>
       </c>
       <c r="I66" s="3">
-        <v>149300</v>
+        <v>150100</v>
       </c>
       <c r="J66" s="3">
+        <v>151700</v>
+      </c>
+      <c r="K66" s="3">
         <v>150700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>148900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>90100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>81500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>68500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>154800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>126400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>133400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>130400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>134600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>177400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>188700</v>
       </c>
     </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3887,8 +4048,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3946,8 +4108,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4005,8 +4170,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4064,8 +4232,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4123,67 +4294,73 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-87900</v>
+        <v>-90400</v>
       </c>
       <c r="E72" s="3">
-        <v>-83900</v>
+        <v>-89300</v>
       </c>
       <c r="F72" s="3">
+        <v>-85300</v>
+      </c>
+      <c r="G72" s="3">
+        <v>-83800</v>
+      </c>
+      <c r="H72" s="3">
+        <v>-84000</v>
+      </c>
+      <c r="I72" s="3">
+        <v>-84800</v>
+      </c>
+      <c r="J72" s="3">
         <v>-82500</v>
       </c>
-      <c r="G72" s="3">
-        <v>-82700</v>
-      </c>
-      <c r="H72" s="3">
-        <v>-83400</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-81200</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-79100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-74600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-73900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-69500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-62200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-64900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-56300</v>
-      </c>
-      <c r="Q72" s="3">
-        <v>-58700</v>
       </c>
       <c r="R72" s="3">
         <v>-58700</v>
       </c>
       <c r="S72" s="3">
+        <v>-58700</v>
+      </c>
+      <c r="T72" s="3">
         <v>-62100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-84300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-79700</v>
       </c>
     </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4241,8 +4418,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4300,8 +4480,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4359,67 +4542,73 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E76" s="3">
         <v>-400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-300</v>
       </c>
-      <c r="H76" s="3">
-        <v>-1000</v>
-      </c>
       <c r="I76" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="J76" s="3">
         <v>500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>10300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>16700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>25300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>5700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>9600</v>
       </c>
     </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4477,131 +4666,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45192</v>
+      </c>
+      <c r="E80" s="2">
         <v>45010</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44828</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44646</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44464</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44282</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43918</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43736</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>43554</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>43372</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>43190</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43001</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>42819</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>42637</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>42455</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>42273</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>42091</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>41909</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-6000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-8300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>15300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-4600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>5300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>3400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-4600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4623,67 +4821,71 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>2200</v>
+      <c r="D83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E83" s="3">
-        <v>1900</v>
+        <v>4200</v>
       </c>
       <c r="F83" s="3">
-        <v>1800</v>
+        <v>-2400</v>
       </c>
       <c r="G83" s="3">
-        <v>2400</v>
+        <v>4300</v>
       </c>
       <c r="H83" s="3">
-        <v>1900</v>
+        <v>-1600</v>
       </c>
       <c r="I83" s="3">
-        <v>2100</v>
+        <v>4000</v>
       </c>
       <c r="J83" s="3">
-        <v>1800</v>
+        <v>-1500</v>
       </c>
       <c r="K83" s="3">
         <v>1800</v>
       </c>
       <c r="L83" s="3">
+        <v>1800</v>
+      </c>
+      <c r="M83" s="3">
         <v>1500</v>
       </c>
-      <c r="M83" s="3" t="s">
+      <c r="N83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1800</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>2000</v>
       </c>
       <c r="R83" s="3">
         <v>2000</v>
       </c>
       <c r="S83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="T83" s="3">
         <v>1900</v>
-      </c>
-      <c r="T83" s="3">
-        <v>3000</v>
       </c>
       <c r="U83" s="3">
         <v>3000</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4741,8 +4943,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4800,8 +5005,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4859,8 +5067,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4918,8 +5129,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4977,67 +5191,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>-1600</v>
+      <c r="D89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E89" s="3">
-        <v>-3500</v>
+        <v>-5100</v>
       </c>
       <c r="F89" s="3">
-        <v>6700</v>
+        <v>-17300</v>
       </c>
       <c r="G89" s="3">
-        <v>6800</v>
+        <v>13800</v>
       </c>
       <c r="H89" s="3">
-        <v>5200</v>
+        <v>8200</v>
       </c>
       <c r="I89" s="3">
-        <v>-6500</v>
+        <v>-1300</v>
       </c>
       <c r="J89" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="K89" s="3">
         <v>1400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1700</v>
       </c>
-      <c r="M89" s="3" t="s">
+      <c r="N89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-13200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-10200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>7300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>9300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-5800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>8500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5059,8 +5279,9 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5086,40 +5307,43 @@
         <v>-2400</v>
       </c>
       <c r="K91" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="L91" s="3">
         <v>-4000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3800</v>
       </c>
-      <c r="M91" s="3" t="s">
+      <c r="N91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1100</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-2400</v>
       </c>
       <c r="T91" s="3">
         <v>-2400</v>
       </c>
       <c r="U91" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="V91" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5177,8 +5401,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5236,67 +5463,73 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>-3300</v>
+      <c r="D94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E94" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="F94" s="3">
+        <v>700</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="H94" s="3">
+        <v>100</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="J94" s="3">
+        <v>4000</v>
+      </c>
+      <c r="K94" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="L94" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="M94" s="3">
         <v>-3600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O94" s="3">
+        <v>102500</v>
+      </c>
+      <c r="P94" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-2100</v>
       </c>
-      <c r="G94" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-700</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N94" s="3">
-        <v>102500</v>
-      </c>
-      <c r="O94" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="P94" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5318,8 +5551,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5377,8 +5611,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5436,8 +5673,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5495,8 +5735,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5554,67 +5797,73 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>4600</v>
+      <c r="D100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E100" s="3">
-        <v>6700</v>
+        <v>11500</v>
       </c>
       <c r="F100" s="3">
-        <v>-5100</v>
+        <v>16200</v>
       </c>
       <c r="G100" s="3">
-        <v>-4100</v>
+        <v>-9300</v>
       </c>
       <c r="H100" s="3">
-        <v>-4200</v>
+        <v>-8600</v>
       </c>
       <c r="I100" s="3">
-        <v>8600</v>
+        <v>4400</v>
       </c>
       <c r="J100" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K100" s="3">
         <v>-400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>7900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1800</v>
       </c>
-      <c r="M100" s="3" t="s">
+      <c r="N100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-72700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>18800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>5100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-8000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>6400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-6500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5649,86 +5898,92 @@
         <v>0</v>
       </c>
       <c r="N101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O101" s="3">
         <v>-100</v>
       </c>
       <c r="P101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
       </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
         <v>-100</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
         <v>-200</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>-200</v>
+      <c r="D102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E102" s="3">
-        <v>-300</v>
+        <v>-600</v>
       </c>
       <c r="F102" s="3">
         <v>-500</v>
       </c>
       <c r="G102" s="3">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="H102" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="I102" s="3">
-        <v>1300</v>
+        <v>900</v>
       </c>
       <c r="J102" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K102" s="3">
         <v>-700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>300</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
-      <c r="M102" s="3" t="s">
+      <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BGI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BGI_QTR_FIN.xlsx
@@ -761,25 +761,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>64900</v>
+        <v>64000</v>
       </c>
       <c r="E8" s="3">
-        <v>61300</v>
+        <v>60400</v>
       </c>
       <c r="F8" s="3">
-        <v>59100</v>
+        <v>58300</v>
       </c>
       <c r="G8" s="3">
-        <v>71500</v>
+        <v>70500</v>
       </c>
       <c r="H8" s="3">
-        <v>62500</v>
+        <v>61700</v>
       </c>
       <c r="I8" s="3">
-        <v>63600</v>
+        <v>62700</v>
       </c>
       <c r="J8" s="3">
-        <v>42100</v>
+        <v>41500</v>
       </c>
       <c r="K8" s="3">
         <v>61100</v>
@@ -823,25 +823,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>38200</v>
+        <v>37700</v>
       </c>
       <c r="E9" s="3">
-        <v>36100</v>
+        <v>35600</v>
       </c>
       <c r="F9" s="3">
-        <v>34100</v>
+        <v>33600</v>
       </c>
       <c r="G9" s="3">
-        <v>40900</v>
+        <v>40400</v>
       </c>
       <c r="H9" s="3">
-        <v>36800</v>
+        <v>36200</v>
       </c>
       <c r="I9" s="3">
-        <v>38800</v>
+        <v>38300</v>
       </c>
       <c r="J9" s="3">
-        <v>25300</v>
+        <v>24900</v>
       </c>
       <c r="K9" s="3">
         <v>38000</v>
@@ -885,25 +885,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>26600</v>
+        <v>26300</v>
       </c>
       <c r="E10" s="3">
-        <v>25200</v>
+        <v>24800</v>
       </c>
       <c r="F10" s="3">
-        <v>25000</v>
+        <v>24700</v>
       </c>
       <c r="G10" s="3">
-        <v>30500</v>
+        <v>30100</v>
       </c>
       <c r="H10" s="3">
-        <v>25800</v>
+        <v>25400</v>
       </c>
       <c r="I10" s="3">
-        <v>24700</v>
+        <v>24400</v>
       </c>
       <c r="J10" s="3">
-        <v>16900</v>
+        <v>16600</v>
       </c>
       <c r="K10" s="3">
         <v>23200</v>
@@ -1160,7 +1160,7 @@
         <v>2300</v>
       </c>
       <c r="E15" s="3">
-        <v>2300</v>
+        <v>2200</v>
       </c>
       <c r="F15" s="3">
         <v>1900</v>
@@ -1169,7 +1169,7 @@
         <v>1800</v>
       </c>
       <c r="H15" s="3">
-        <v>2500</v>
+        <v>2400</v>
       </c>
       <c r="I15" s="3">
         <v>1900</v>
@@ -1243,22 +1243,22 @@
         <v>4</v>
       </c>
       <c r="E17" s="3">
-        <v>63600</v>
+        <v>62700</v>
       </c>
       <c r="F17" s="3">
-        <v>59600</v>
+        <v>58800</v>
       </c>
       <c r="G17" s="3">
-        <v>70200</v>
+        <v>69200</v>
       </c>
       <c r="H17" s="3">
-        <v>60600</v>
+        <v>59700</v>
       </c>
       <c r="I17" s="3">
-        <v>64600</v>
+        <v>63700</v>
       </c>
       <c r="J17" s="3">
-        <v>43200</v>
+        <v>42600</v>
       </c>
       <c r="K17" s="3">
         <v>64400</v>
@@ -1314,7 +1314,7 @@
         <v>1300</v>
       </c>
       <c r="H18" s="3">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="I18" s="3">
         <v>-1100</v>
@@ -1391,7 +1391,7 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="F20" s="3">
         <v>700</v>
@@ -1456,16 +1456,16 @@
         <v>2600</v>
       </c>
       <c r="F21" s="3">
-        <v>-2200</v>
+        <v>-2100</v>
       </c>
       <c r="G21" s="3">
-        <v>5600</v>
+        <v>5500</v>
       </c>
       <c r="H21" s="3">
         <v>400</v>
       </c>
       <c r="I21" s="3">
-        <v>3000</v>
+        <v>2900</v>
       </c>
       <c r="J21" s="3">
         <v>-2500</v>
@@ -1512,7 +1512,7 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>2500</v>
+        <v>2400</v>
       </c>
       <c r="E22" s="3">
         <v>2400</v>
@@ -1530,7 +1530,7 @@
         <v>1200</v>
       </c>
       <c r="J22" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="K22" s="3">
         <v>2400</v>
@@ -2135,7 +2135,7 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
-        <v>-800</v>
+        <v>-700</v>
       </c>
       <c r="F32" s="3">
         <v>-700</v>
@@ -2501,7 +2501,7 @@
         <v>900</v>
       </c>
       <c r="F41" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="G41" s="3">
         <v>1500</v>
@@ -2619,22 +2619,22 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>6700</v>
+        <v>6600</v>
       </c>
       <c r="E43" s="3">
-        <v>8400</v>
+        <v>8300</v>
       </c>
       <c r="F43" s="3">
-        <v>9000</v>
+        <v>8800</v>
       </c>
       <c r="G43" s="3">
         <v>5900</v>
       </c>
       <c r="H43" s="3">
-        <v>6000</v>
+        <v>5900</v>
       </c>
       <c r="I43" s="3">
-        <v>5400</v>
+        <v>5300</v>
       </c>
       <c r="J43" s="3">
         <v>4600</v>
@@ -2681,25 +2681,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>68000</v>
+        <v>67100</v>
       </c>
       <c r="E44" s="3">
-        <v>65300</v>
+        <v>64400</v>
       </c>
       <c r="F44" s="3">
-        <v>57600</v>
+        <v>56800</v>
       </c>
       <c r="G44" s="3">
-        <v>58300</v>
+        <v>57500</v>
       </c>
       <c r="H44" s="3">
-        <v>65400</v>
+        <v>64500</v>
       </c>
       <c r="I44" s="3">
-        <v>72300</v>
+        <v>71300</v>
       </c>
       <c r="J44" s="3">
-        <v>74100</v>
+        <v>73100</v>
       </c>
       <c r="K44" s="3">
         <v>74100</v>
@@ -2749,7 +2749,7 @@
         <v>2000</v>
       </c>
       <c r="F45" s="3">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="G45" s="3">
         <v>1300</v>
@@ -2805,25 +2805,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>78200</v>
+        <v>77100</v>
       </c>
       <c r="E46" s="3">
-        <v>76600</v>
+        <v>75600</v>
       </c>
       <c r="F46" s="3">
-        <v>69600</v>
+        <v>68700</v>
       </c>
       <c r="G46" s="3">
-        <v>67100</v>
+        <v>66200</v>
       </c>
       <c r="H46" s="3">
-        <v>75000</v>
+        <v>73900</v>
       </c>
       <c r="I46" s="3">
-        <v>80500</v>
+        <v>79400</v>
       </c>
       <c r="J46" s="3">
-        <v>82100</v>
+        <v>80900</v>
       </c>
       <c r="K46" s="3">
         <v>80300</v>
@@ -2867,13 +2867,13 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>3600</v>
+        <v>3500</v>
       </c>
       <c r="E47" s="3">
         <v>2900</v>
       </c>
       <c r="F47" s="3">
-        <v>3400</v>
+        <v>3300</v>
       </c>
       <c r="G47" s="3">
         <v>4100</v>
@@ -2882,10 +2882,10 @@
         <v>4200</v>
       </c>
       <c r="I47" s="3">
-        <v>4200</v>
+        <v>4100</v>
       </c>
       <c r="J47" s="3">
-        <v>3500</v>
+        <v>3400</v>
       </c>
       <c r="K47" s="3">
         <v>3300</v>
@@ -2929,25 +2929,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>58400</v>
+        <v>57600</v>
       </c>
       <c r="E48" s="3">
-        <v>60800</v>
+        <v>60000</v>
       </c>
       <c r="F48" s="3">
-        <v>60600</v>
+        <v>59800</v>
       </c>
       <c r="G48" s="3">
-        <v>59700</v>
+        <v>58900</v>
       </c>
       <c r="H48" s="3">
-        <v>60700</v>
+        <v>59900</v>
       </c>
       <c r="I48" s="3">
-        <v>60700</v>
+        <v>59900</v>
       </c>
       <c r="J48" s="3">
-        <v>63000</v>
+        <v>62200</v>
       </c>
       <c r="K48" s="3">
         <v>65900</v>
@@ -2991,19 +2991,19 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>5600</v>
+        <v>5500</v>
       </c>
       <c r="E49" s="3">
-        <v>5200</v>
+        <v>5100</v>
       </c>
       <c r="F49" s="3">
+        <v>4300</v>
+      </c>
+      <c r="G49" s="3">
         <v>4400</v>
       </c>
-      <c r="G49" s="3">
-        <v>4500</v>
-      </c>
       <c r="H49" s="3">
-        <v>4100</v>
+        <v>4000</v>
       </c>
       <c r="I49" s="3">
         <v>3600</v>
@@ -3301,25 +3301,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>145800</v>
+        <v>143800</v>
       </c>
       <c r="E54" s="3">
-        <v>145600</v>
+        <v>143600</v>
       </c>
       <c r="F54" s="3">
-        <v>138000</v>
+        <v>136100</v>
       </c>
       <c r="G54" s="3">
-        <v>135400</v>
+        <v>133600</v>
       </c>
       <c r="H54" s="3">
-        <v>144000</v>
+        <v>142100</v>
       </c>
       <c r="I54" s="3">
-        <v>149000</v>
+        <v>147000</v>
       </c>
       <c r="J54" s="3">
-        <v>152200</v>
+        <v>150100</v>
       </c>
       <c r="K54" s="3">
         <v>153100</v>
@@ -3411,25 +3411,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>28500</v>
+        <v>28100</v>
       </c>
       <c r="E57" s="3">
-        <v>27800</v>
+        <v>27400</v>
       </c>
       <c r="F57" s="3">
-        <v>19900</v>
+        <v>19600</v>
       </c>
       <c r="G57" s="3">
-        <v>20900</v>
+        <v>20600</v>
       </c>
       <c r="H57" s="3">
-        <v>25600</v>
+        <v>25300</v>
       </c>
       <c r="I57" s="3">
-        <v>28100</v>
+        <v>27700</v>
       </c>
       <c r="J57" s="3">
-        <v>26700</v>
+        <v>26300</v>
       </c>
       <c r="K57" s="3">
         <v>35000</v>
@@ -3473,25 +3473,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>47200</v>
+        <v>46500</v>
       </c>
       <c r="E58" s="3">
-        <v>44400</v>
+        <v>43700</v>
       </c>
       <c r="F58" s="3">
-        <v>39800</v>
+        <v>39200</v>
       </c>
       <c r="G58" s="3">
-        <v>33500</v>
+        <v>33000</v>
       </c>
       <c r="H58" s="3">
-        <v>38100</v>
+        <v>37600</v>
       </c>
       <c r="I58" s="3">
-        <v>41600</v>
+        <v>41100</v>
       </c>
       <c r="J58" s="3">
-        <v>46200</v>
+        <v>45600</v>
       </c>
       <c r="K58" s="3">
         <v>42200</v>
@@ -3535,25 +3535,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>9200</v>
+        <v>9100</v>
       </c>
       <c r="E59" s="3">
-        <v>10600</v>
+        <v>10500</v>
       </c>
       <c r="F59" s="3">
-        <v>10100</v>
+        <v>10000</v>
       </c>
       <c r="G59" s="3">
-        <v>11300</v>
+        <v>11200</v>
       </c>
       <c r="H59" s="3">
+        <v>12700</v>
+      </c>
+      <c r="I59" s="3">
         <v>12800</v>
       </c>
-      <c r="I59" s="3">
-        <v>12900</v>
-      </c>
       <c r="J59" s="3">
-        <v>9500</v>
+        <v>9400</v>
       </c>
       <c r="K59" s="3">
         <v>7600</v>
@@ -3597,25 +3597,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>84900</v>
+        <v>83700</v>
       </c>
       <c r="E60" s="3">
-        <v>82800</v>
+        <v>81700</v>
       </c>
       <c r="F60" s="3">
-        <v>69800</v>
+        <v>68800</v>
       </c>
       <c r="G60" s="3">
-        <v>65700</v>
+        <v>64800</v>
       </c>
       <c r="H60" s="3">
-        <v>76500</v>
+        <v>75500</v>
       </c>
       <c r="I60" s="3">
-        <v>82600</v>
+        <v>81500</v>
       </c>
       <c r="J60" s="3">
-        <v>82500</v>
+        <v>81300</v>
       </c>
       <c r="K60" s="3">
         <v>84900</v>
@@ -3659,25 +3659,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>17100</v>
+        <v>16900</v>
       </c>
       <c r="E61" s="3">
-        <v>16400</v>
+        <v>16200</v>
       </c>
       <c r="F61" s="3">
+        <v>16000</v>
+      </c>
+      <c r="G61" s="3">
+        <v>15600</v>
+      </c>
+      <c r="H61" s="3">
         <v>16300</v>
       </c>
-      <c r="G61" s="3">
-        <v>15800</v>
-      </c>
-      <c r="H61" s="3">
-        <v>16500</v>
-      </c>
       <c r="I61" s="3">
-        <v>17000</v>
+        <v>16800</v>
       </c>
       <c r="J61" s="3">
-        <v>17400</v>
+        <v>17200</v>
       </c>
       <c r="K61" s="3">
         <v>11800</v>
@@ -3721,25 +3721,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>45300</v>
+        <v>44600</v>
       </c>
       <c r="E62" s="3">
-        <v>46800</v>
+        <v>46200</v>
       </c>
       <c r="F62" s="3">
-        <v>48800</v>
+        <v>48100</v>
       </c>
       <c r="G62" s="3">
-        <v>49600</v>
+        <v>48900</v>
       </c>
       <c r="H62" s="3">
-        <v>51300</v>
+        <v>50600</v>
       </c>
       <c r="I62" s="3">
-        <v>50400</v>
+        <v>49700</v>
       </c>
       <c r="J62" s="3">
-        <v>51900</v>
+        <v>51200</v>
       </c>
       <c r="K62" s="3">
         <v>54000</v>
@@ -3969,25 +3969,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>147300</v>
+        <v>145300</v>
       </c>
       <c r="E66" s="3">
-        <v>146000</v>
+        <v>144000</v>
       </c>
       <c r="F66" s="3">
-        <v>134800</v>
+        <v>132900</v>
       </c>
       <c r="G66" s="3">
-        <v>131100</v>
+        <v>129300</v>
       </c>
       <c r="H66" s="3">
-        <v>144400</v>
+        <v>142400</v>
       </c>
       <c r="I66" s="3">
-        <v>150100</v>
+        <v>148000</v>
       </c>
       <c r="J66" s="3">
-        <v>151700</v>
+        <v>149600</v>
       </c>
       <c r="K66" s="3">
         <v>150700</v>
@@ -4303,25 +4303,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-90400</v>
+        <v>-89200</v>
       </c>
       <c r="E72" s="3">
-        <v>-89300</v>
+        <v>-88100</v>
       </c>
       <c r="F72" s="3">
-        <v>-85300</v>
+        <v>-84100</v>
       </c>
       <c r="G72" s="3">
-        <v>-83800</v>
+        <v>-82700</v>
       </c>
       <c r="H72" s="3">
-        <v>-84000</v>
+        <v>-82900</v>
       </c>
       <c r="I72" s="3">
-        <v>-84800</v>
+        <v>-83600</v>
       </c>
       <c r="J72" s="3">
-        <v>-82500</v>
+        <v>-81400</v>
       </c>
       <c r="K72" s="3">
         <v>-79100</v>
@@ -4566,7 +4566,7 @@
         <v>-300</v>
       </c>
       <c r="I76" s="3">
-        <v>-1100</v>
+        <v>-1000</v>
       </c>
       <c r="J76" s="3">
         <v>500</v>
@@ -4831,13 +4831,13 @@
         <v>4</v>
       </c>
       <c r="E83" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F83" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="G83" s="3">
         <v>4200</v>
-      </c>
-      <c r="F83" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="G83" s="3">
-        <v>4300</v>
       </c>
       <c r="H83" s="3">
         <v>-1600</v>
@@ -5203,22 +5203,22 @@
         <v>4</v>
       </c>
       <c r="E89" s="3">
-        <v>-5100</v>
+        <v>-5000</v>
       </c>
       <c r="F89" s="3">
-        <v>-17300</v>
+        <v>-17100</v>
       </c>
       <c r="G89" s="3">
-        <v>13800</v>
+        <v>13600</v>
       </c>
       <c r="H89" s="3">
-        <v>8200</v>
+        <v>8100</v>
       </c>
       <c r="I89" s="3">
         <v>-1300</v>
       </c>
       <c r="J89" s="3">
-        <v>-3400</v>
+        <v>-3300</v>
       </c>
       <c r="K89" s="3">
         <v>1400</v>
@@ -5475,13 +5475,13 @@
         <v>4</v>
       </c>
       <c r="E94" s="3">
-        <v>-7000</v>
+        <v>-6900</v>
       </c>
       <c r="F94" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="G94" s="3">
-        <v>-4300</v>
+        <v>-4200</v>
       </c>
       <c r="H94" s="3">
         <v>100</v>
@@ -5490,7 +5490,7 @@
         <v>-2200</v>
       </c>
       <c r="J94" s="3">
-        <v>4000</v>
+        <v>3900</v>
       </c>
       <c r="K94" s="3">
         <v>-1800</v>
@@ -5809,19 +5809,19 @@
         <v>4</v>
       </c>
       <c r="E100" s="3">
-        <v>11500</v>
+        <v>11400</v>
       </c>
       <c r="F100" s="3">
-        <v>16200</v>
+        <v>16000</v>
       </c>
       <c r="G100" s="3">
-        <v>-9300</v>
+        <v>-9200</v>
       </c>
       <c r="H100" s="3">
-        <v>-8600</v>
+        <v>-8400</v>
       </c>
       <c r="I100" s="3">
-        <v>4400</v>
+        <v>4300</v>
       </c>
       <c r="J100" s="3">
         <v>1200</v>
@@ -5933,7 +5933,7 @@
         <v>4</v>
       </c>
       <c r="E102" s="3">
-        <v>-600</v>
+        <v>-500</v>
       </c>
       <c r="F102" s="3">
         <v>-500</v>

--- a/AAII_Financials/Quarterly/BGI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BGI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
   <si>
     <t>BGI</t>
   </si>
@@ -656,293 +656,306 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E7" s="2">
         <v>45192</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45010</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44828</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44646</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44464</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44282</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43918</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>43736</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>43554</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>43372</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43190</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43001</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>42819</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>42637</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>42455</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>42273</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>42091</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>41909</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>64000</v>
+        <v>71800</v>
       </c>
       <c r="E8" s="3">
-        <v>60400</v>
+        <v>64600</v>
       </c>
       <c r="F8" s="3">
-        <v>58300</v>
+        <v>61000</v>
       </c>
       <c r="G8" s="3">
-        <v>70500</v>
+        <v>58900</v>
       </c>
       <c r="H8" s="3">
-        <v>61700</v>
+        <v>71200</v>
       </c>
       <c r="I8" s="3">
-        <v>62700</v>
+        <v>62300</v>
       </c>
       <c r="J8" s="3">
+        <v>63300</v>
+      </c>
+      <c r="K8" s="3">
         <v>41500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>61100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>63200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>61800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>52700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>63500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>54000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>46900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>39900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>113000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>99700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>161900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>139700</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>37700</v>
+        <v>44100</v>
       </c>
       <c r="E9" s="3">
-        <v>35600</v>
+        <v>38100</v>
       </c>
       <c r="F9" s="3">
-        <v>33600</v>
+        <v>35900</v>
       </c>
       <c r="G9" s="3">
-        <v>40400</v>
+        <v>34000</v>
       </c>
       <c r="H9" s="3">
-        <v>36200</v>
+        <v>40800</v>
       </c>
       <c r="I9" s="3">
-        <v>38300</v>
+        <v>36600</v>
       </c>
       <c r="J9" s="3">
+        <v>38700</v>
+      </c>
+      <c r="K9" s="3">
         <v>24900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>38000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>39100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>37600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>32500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>40500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>32300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>28400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>23500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>70000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>61300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>99500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>84300</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>26300</v>
+        <v>27600</v>
       </c>
       <c r="E10" s="3">
-        <v>24800</v>
+        <v>26500</v>
       </c>
       <c r="F10" s="3">
-        <v>24700</v>
+        <v>25100</v>
       </c>
       <c r="G10" s="3">
-        <v>30100</v>
+        <v>24900</v>
       </c>
       <c r="H10" s="3">
-        <v>25400</v>
+        <v>30400</v>
       </c>
       <c r="I10" s="3">
-        <v>24400</v>
+        <v>25700</v>
       </c>
       <c r="J10" s="3">
+        <v>24600</v>
+      </c>
+      <c r="K10" s="3">
         <v>16600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>23200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>24100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>24200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>20200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>23100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>21600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>18500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>16400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>43000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>38400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>62400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>55400</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -965,8 +978,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1027,8 +1041,11 @@
       <c r="V12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1089,8 +1106,11 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1109,112 +1129,118 @@
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="3">
         <v>200</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>2900</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>500</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>5500</v>
       </c>
-      <c r="V14" s="3" t="s">
+      <c r="W14" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E15" s="3">
         <v>2300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2100</v>
-      </c>
-      <c r="K15" s="3">
-        <v>1800</v>
       </c>
       <c r="L15" s="3">
         <v>1800</v>
       </c>
       <c r="M15" s="3">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="N15" s="3">
         <v>1500</v>
       </c>
       <c r="O15" s="3">
+        <v>1500</v>
+      </c>
+      <c r="P15" s="3">
         <v>1300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>1100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>2000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>2900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1234,132 +1260,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>4</v>
+      <c r="D17" s="3">
+        <v>71200</v>
       </c>
       <c r="E17" s="3">
-        <v>62700</v>
+        <v>64300</v>
       </c>
       <c r="F17" s="3">
+        <v>63300</v>
+      </c>
+      <c r="G17" s="3">
+        <v>59400</v>
+      </c>
+      <c r="H17" s="3">
+        <v>69900</v>
+      </c>
+      <c r="I17" s="3">
+        <v>60300</v>
+      </c>
+      <c r="J17" s="3">
+        <v>64400</v>
+      </c>
+      <c r="K17" s="3">
+        <v>42600</v>
+      </c>
+      <c r="L17" s="3">
+        <v>64400</v>
+      </c>
+      <c r="M17" s="3">
+        <v>64700</v>
+      </c>
+      <c r="N17" s="3">
+        <v>65700</v>
+      </c>
+      <c r="O17" s="3">
+        <v>59200</v>
+      </c>
+      <c r="P17" s="3">
+        <v>73000</v>
+      </c>
+      <c r="Q17" s="3">
         <v>58800</v>
       </c>
-      <c r="G17" s="3">
-        <v>69200</v>
-      </c>
-      <c r="H17" s="3">
-        <v>59700</v>
-      </c>
-      <c r="I17" s="3">
-        <v>63700</v>
-      </c>
-      <c r="J17" s="3">
-        <v>42600</v>
-      </c>
-      <c r="K17" s="3">
-        <v>64400</v>
-      </c>
-      <c r="L17" s="3">
-        <v>64700</v>
-      </c>
-      <c r="M17" s="3">
-        <v>65700</v>
-      </c>
-      <c r="N17" s="3">
-        <v>59200</v>
-      </c>
-      <c r="O17" s="3">
-        <v>73000</v>
-      </c>
-      <c r="P17" s="3">
-        <v>58800</v>
-      </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>48100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>41300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>106000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>95200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>161900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>137000</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>4</v>
+      <c r="D18" s="3">
+        <v>600</v>
       </c>
       <c r="E18" s="3">
+        <v>400</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1300</v>
       </c>
-      <c r="H18" s="3">
-        <v>1900</v>
-      </c>
       <c r="I18" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J18" s="3">
         <v>-1100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-3200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-3900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-6500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-9500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>7000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>4500</v>
       </c>
-      <c r="U18" s="3">
-        <v>0</v>
-      </c>
       <c r="V18" s="3">
+        <v>0</v>
+      </c>
+      <c r="W18" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1382,23 +1415,24 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3">
+        <v>600</v>
       </c>
       <c r="E20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F20" s="3">
+        <v>800</v>
+      </c>
+      <c r="G20" s="3">
         <v>700</v>
       </c>
-      <c r="F20" s="3">
-        <v>700</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
         <v>0</v>
       </c>
@@ -1444,194 +1478,206 @@
       <c r="V20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>3700</v>
+      </c>
+      <c r="F21" s="3">
+        <v>700</v>
+      </c>
+      <c r="G21" s="3">
+        <v>2100</v>
+      </c>
+      <c r="H21" s="3">
+        <v>3200</v>
+      </c>
+      <c r="I21" s="3">
+        <v>4400</v>
+      </c>
+      <c r="J21" s="3">
+        <v>900</v>
+      </c>
+      <c r="K21" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="L21" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="M21" s="3">
+        <v>300</v>
+      </c>
+      <c r="N21" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E21" s="3">
-        <v>2600</v>
-      </c>
-      <c r="F21" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="G21" s="3">
-        <v>5500</v>
-      </c>
-      <c r="H21" s="3">
-        <v>400</v>
-      </c>
-      <c r="I21" s="3">
-        <v>2900</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="L21" s="3">
-        <v>300</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-8200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-3500</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>-400</v>
       </c>
       <c r="R21" s="3">
         <v>-400</v>
       </c>
       <c r="S21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="T21" s="3">
         <v>7200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>6400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E22" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F22" s="3">
         <v>2400</v>
       </c>
-      <c r="E22" s="3">
-        <v>2400</v>
-      </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1100</v>
-      </c>
-      <c r="H22" s="3">
-        <v>1200</v>
       </c>
       <c r="I22" s="3">
         <v>1200</v>
       </c>
       <c r="J22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K22" s="3">
         <v>1000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>2400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>2100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>2000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>3600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>3900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>4600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-4000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-3300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-6000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-7900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-11400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-4600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1692,8 +1738,11 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1754,132 +1803,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>4</v>
+      <c r="D26" s="3">
+        <v>-2300</v>
       </c>
       <c r="E26" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F26" s="3">
         <v>-4000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-3300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-6000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-7900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-11400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>3400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-4600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>4</v>
+      <c r="D27" s="3">
+        <v>-2300</v>
       </c>
       <c r="E27" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F27" s="3">
         <v>-4000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-3300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-6000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-7900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-11400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>3400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-4600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1940,8 +1998,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1960,50 +2021,53 @@
       <c r="H29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
+      <c r="I29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
       </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>-300</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-100</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>-300</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>26700</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>1500</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>7600</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>1500</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
+      <c r="U29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2064,8 +2128,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2126,23 +2193,26 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3">
+        <v>-600</v>
       </c>
       <c r="E32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="G32" s="3">
         <v>-700</v>
       </c>
-      <c r="F32" s="3">
-        <v>-700</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
@@ -2188,70 +2258,76 @@
       <c r="V32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>4</v>
+      <c r="D33" s="3">
+        <v>-2300</v>
       </c>
       <c r="E33" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F33" s="3">
         <v>-4000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-6000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-3400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-5900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-8300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>15300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>5300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>3400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-4600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2312,137 +2388,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>4</v>
+      <c r="D35" s="3">
+        <v>-2300</v>
       </c>
       <c r="E35" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F35" s="3">
         <v>-4000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-6000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-3400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-5900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-8300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>15300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>5300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>3400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-4600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E38" s="2">
         <v>45192</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45010</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44828</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44646</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44464</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44282</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43918</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>43736</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>43554</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>43372</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43190</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43001</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>42819</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>42637</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>42455</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>42273</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>42091</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>41909</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2465,8 +2550,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2489,70 +2575,74 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E41" s="3">
         <v>1500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>900</v>
       </c>
-      <c r="F41" s="3">
-        <v>1100</v>
-      </c>
       <c r="G41" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H41" s="3">
         <v>1500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1200</v>
-      </c>
-      <c r="M41" s="3">
-        <v>900</v>
       </c>
       <c r="N41" s="3">
         <v>900</v>
       </c>
       <c r="O41" s="3">
+        <v>900</v>
+      </c>
+      <c r="P41" s="3">
         <v>800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2613,152 +2703,161 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E43" s="3">
         <v>6600</v>
       </c>
-      <c r="E43" s="3">
-        <v>8300</v>
-      </c>
       <c r="F43" s="3">
-        <v>8800</v>
+        <v>8400</v>
       </c>
       <c r="G43" s="3">
-        <v>5900</v>
+        <v>8900</v>
       </c>
       <c r="H43" s="3">
         <v>5900</v>
       </c>
       <c r="I43" s="3">
-        <v>5300</v>
+        <v>6000</v>
       </c>
       <c r="J43" s="3">
+        <v>5400</v>
+      </c>
+      <c r="K43" s="3">
         <v>4600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>10300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>7300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>7700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>6800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>7700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>67100</v>
+        <v>72900</v>
       </c>
       <c r="E44" s="3">
-        <v>64400</v>
+        <v>67700</v>
       </c>
       <c r="F44" s="3">
-        <v>56800</v>
+        <v>65000</v>
       </c>
       <c r="G44" s="3">
-        <v>57500</v>
+        <v>57300</v>
       </c>
       <c r="H44" s="3">
-        <v>64500</v>
+        <v>58100</v>
       </c>
       <c r="I44" s="3">
-        <v>71300</v>
+        <v>65200</v>
       </c>
       <c r="J44" s="3">
+        <v>72000</v>
+      </c>
+      <c r="K44" s="3">
         <v>73100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>74100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>75300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>68700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>67900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>66100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>59700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>100500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>103800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>102600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>101300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>135700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>150400</v>
       </c>
     </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="E45" s="3">
         <v>2000</v>
       </c>
       <c r="F45" s="3">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="G45" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H45" s="3">
         <v>1300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1600</v>
-      </c>
-      <c r="I45" s="3">
-        <v>1500</v>
       </c>
       <c r="J45" s="3">
         <v>1500</v>
@@ -2770,140 +2869,146 @@
         <v>1500</v>
       </c>
       <c r="M45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="N45" s="3">
         <v>1600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>82200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>77100</v>
+        <v>82600</v>
       </c>
       <c r="E46" s="3">
+        <v>77900</v>
+      </c>
+      <c r="F46" s="3">
+        <v>76300</v>
+      </c>
+      <c r="G46" s="3">
+        <v>69400</v>
+      </c>
+      <c r="H46" s="3">
+        <v>66800</v>
+      </c>
+      <c r="I46" s="3">
+        <v>74700</v>
+      </c>
+      <c r="J46" s="3">
+        <v>80200</v>
+      </c>
+      <c r="K46" s="3">
+        <v>80900</v>
+      </c>
+      <c r="L46" s="3">
+        <v>80300</v>
+      </c>
+      <c r="M46" s="3">
+        <v>82500</v>
+      </c>
+      <c r="N46" s="3">
+        <v>73900</v>
+      </c>
+      <c r="O46" s="3">
+        <v>74500</v>
+      </c>
+      <c r="P46" s="3">
         <v>75600</v>
       </c>
-      <c r="F46" s="3">
-        <v>68700</v>
-      </c>
-      <c r="G46" s="3">
-        <v>66200</v>
-      </c>
-      <c r="H46" s="3">
-        <v>73900</v>
-      </c>
-      <c r="I46" s="3">
-        <v>79400</v>
-      </c>
-      <c r="J46" s="3">
-        <v>80900</v>
-      </c>
-      <c r="K46" s="3">
-        <v>80300</v>
-      </c>
-      <c r="L46" s="3">
-        <v>82500</v>
-      </c>
-      <c r="M46" s="3">
-        <v>73900</v>
-      </c>
-      <c r="N46" s="3">
-        <v>74500</v>
-      </c>
-      <c r="O46" s="3">
-        <v>75600</v>
-      </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>147700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>114000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>115600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>113300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>112500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>148000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>162600</v>
       </c>
     </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>3500</v>
+        <v>4200</v>
       </c>
       <c r="E47" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F47" s="3">
         <v>2900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
+        <v>3400</v>
+      </c>
+      <c r="H47" s="3">
+        <v>4100</v>
+      </c>
+      <c r="I47" s="3">
+        <v>4200</v>
+      </c>
+      <c r="J47" s="3">
+        <v>4200</v>
+      </c>
+      <c r="K47" s="3">
+        <v>3400</v>
+      </c>
+      <c r="L47" s="3">
         <v>3300</v>
       </c>
-      <c r="G47" s="3">
-        <v>4100</v>
-      </c>
-      <c r="H47" s="3">
-        <v>4200</v>
-      </c>
-      <c r="I47" s="3">
-        <v>4100</v>
-      </c>
-      <c r="J47" s="3">
-        <v>3400</v>
-      </c>
-      <c r="K47" s="3">
-        <v>3300</v>
-      </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>700</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>4</v>
+      <c r="P47" s="3">
+        <v>0</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>4</v>
@@ -2917,96 +3022,102 @@
       <c r="T47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U47" s="3">
-        <v>0</v>
+      <c r="U47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>57600</v>
+        <v>57000</v>
       </c>
       <c r="E48" s="3">
-        <v>60000</v>
+        <v>58200</v>
       </c>
       <c r="F48" s="3">
-        <v>59800</v>
+        <v>60600</v>
       </c>
       <c r="G48" s="3">
-        <v>58900</v>
+        <v>60400</v>
       </c>
       <c r="H48" s="3">
-        <v>59900</v>
+        <v>59500</v>
       </c>
       <c r="I48" s="3">
-        <v>59900</v>
+        <v>60500</v>
       </c>
       <c r="J48" s="3">
+        <v>60500</v>
+      </c>
+      <c r="K48" s="3">
         <v>62200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>65900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>68900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>22300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>18400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>15100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>11900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>17500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>21200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>21900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>22100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>28500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>31700</v>
       </c>
     </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>5500</v>
+        <v>5800</v>
       </c>
       <c r="E49" s="3">
-        <v>5100</v>
+        <v>5600</v>
       </c>
       <c r="F49" s="3">
-        <v>4300</v>
+        <v>5200</v>
       </c>
       <c r="G49" s="3">
         <v>4400</v>
       </c>
       <c r="H49" s="3">
-        <v>4000</v>
+        <v>4400</v>
       </c>
       <c r="I49" s="3">
-        <v>3600</v>
+        <v>4100</v>
       </c>
       <c r="J49" s="3">
         <v>3600</v>
@@ -3015,40 +3126,43 @@
         <v>3600</v>
       </c>
       <c r="L49" s="3">
+        <v>3600</v>
+      </c>
+      <c r="M49" s="3">
         <v>3200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2800</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>500</v>
       </c>
       <c r="R49" s="3">
         <v>500</v>
       </c>
       <c r="S49" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="T49" s="3">
         <v>600</v>
       </c>
       <c r="U49" s="3">
+        <v>600</v>
+      </c>
+      <c r="V49" s="3">
         <v>900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3109,8 +3223,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3171,8 +3288,11 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3216,25 +3336,28 @@
         <v>0</v>
       </c>
       <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3">
         <v>4200</v>
-      </c>
-      <c r="R52" s="3">
-        <v>400</v>
       </c>
       <c r="S52" s="3">
         <v>400</v>
       </c>
       <c r="T52" s="3">
+        <v>400</v>
+      </c>
+      <c r="U52" s="3">
         <v>1600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3295,70 +3418,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>143800</v>
+        <v>149600</v>
       </c>
       <c r="E54" s="3">
-        <v>143600</v>
+        <v>145200</v>
       </c>
       <c r="F54" s="3">
-        <v>136100</v>
+        <v>145000</v>
       </c>
       <c r="G54" s="3">
-        <v>133600</v>
+        <v>137500</v>
       </c>
       <c r="H54" s="3">
-        <v>142100</v>
+        <v>134900</v>
       </c>
       <c r="I54" s="3">
-        <v>147000</v>
+        <v>143500</v>
       </c>
       <c r="J54" s="3">
+        <v>148500</v>
+      </c>
+      <c r="K54" s="3">
         <v>150100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>153100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>157600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>100500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>98200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>93800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>162300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>136200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>137700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>136200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>136800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>180200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>198300</v>
       </c>
     </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3381,8 +3510,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3405,380 +3535,399 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>28100</v>
+        <v>31700</v>
       </c>
       <c r="E57" s="3">
-        <v>27400</v>
+        <v>28400</v>
       </c>
       <c r="F57" s="3">
-        <v>19600</v>
+        <v>27700</v>
       </c>
       <c r="G57" s="3">
+        <v>19800</v>
+      </c>
+      <c r="H57" s="3">
+        <v>20800</v>
+      </c>
+      <c r="I57" s="3">
+        <v>25500</v>
+      </c>
+      <c r="J57" s="3">
+        <v>28000</v>
+      </c>
+      <c r="K57" s="3">
+        <v>26300</v>
+      </c>
+      <c r="L57" s="3">
+        <v>35000</v>
+      </c>
+      <c r="M57" s="3">
+        <v>29700</v>
+      </c>
+      <c r="N57" s="3">
+        <v>25000</v>
+      </c>
+      <c r="O57" s="3">
+        <v>20800</v>
+      </c>
+      <c r="P57" s="3">
         <v>20600</v>
       </c>
-      <c r="H57" s="3">
-        <v>25300</v>
-      </c>
-      <c r="I57" s="3">
-        <v>27700</v>
-      </c>
-      <c r="J57" s="3">
-        <v>26300</v>
-      </c>
-      <c r="K57" s="3">
-        <v>35000</v>
-      </c>
-      <c r="L57" s="3">
-        <v>29700</v>
-      </c>
-      <c r="M57" s="3">
-        <v>25000</v>
-      </c>
-      <c r="N57" s="3">
-        <v>20800</v>
-      </c>
-      <c r="O57" s="3">
-        <v>20600</v>
-      </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>19000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>35500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>35100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>34800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>31800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>44700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>46000</v>
       </c>
     </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>46500</v>
+        <v>49900</v>
       </c>
       <c r="E58" s="3">
-        <v>43700</v>
+        <v>47000</v>
       </c>
       <c r="F58" s="3">
-        <v>39200</v>
+        <v>44200</v>
       </c>
       <c r="G58" s="3">
-        <v>33000</v>
+        <v>39600</v>
       </c>
       <c r="H58" s="3">
-        <v>37600</v>
+        <v>33300</v>
       </c>
       <c r="I58" s="3">
-        <v>41100</v>
+        <v>37900</v>
       </c>
       <c r="J58" s="3">
+        <v>41500</v>
+      </c>
+      <c r="K58" s="3">
         <v>45600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>42200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>44800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>36100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>36000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>31400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>46100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>55700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>56800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>50700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>58200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>69100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>79600</v>
       </c>
     </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>9100</v>
+        <v>9200</v>
       </c>
       <c r="E59" s="3">
-        <v>10500</v>
+        <v>9200</v>
       </c>
       <c r="F59" s="3">
-        <v>10000</v>
+        <v>10600</v>
       </c>
       <c r="G59" s="3">
-        <v>11200</v>
+        <v>10100</v>
       </c>
       <c r="H59" s="3">
-        <v>12700</v>
+        <v>11300</v>
       </c>
       <c r="I59" s="3">
         <v>12800</v>
       </c>
       <c r="J59" s="3">
+        <v>12900</v>
+      </c>
+      <c r="K59" s="3">
         <v>9400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>8900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>79300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>5600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>6700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>5700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>8100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>83700</v>
+        <v>90700</v>
       </c>
       <c r="E60" s="3">
-        <v>81700</v>
+        <v>84600</v>
       </c>
       <c r="F60" s="3">
-        <v>68800</v>
+        <v>82500</v>
       </c>
       <c r="G60" s="3">
-        <v>64800</v>
+        <v>69500</v>
       </c>
       <c r="H60" s="3">
-        <v>75500</v>
+        <v>65400</v>
       </c>
       <c r="I60" s="3">
-        <v>81500</v>
+        <v>76200</v>
       </c>
       <c r="J60" s="3">
+        <v>82300</v>
+      </c>
+      <c r="K60" s="3">
         <v>81300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>84900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>83500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>68300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>63400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>57800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>144500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>97600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>97500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>92200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>95700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>121900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>133400</v>
       </c>
     </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>16900</v>
+        <v>16600</v>
       </c>
       <c r="E61" s="3">
+        <v>17100</v>
+      </c>
+      <c r="F61" s="3">
+        <v>16300</v>
+      </c>
+      <c r="G61" s="3">
         <v>16200</v>
       </c>
-      <c r="F61" s="3">
-        <v>16000</v>
-      </c>
-      <c r="G61" s="3">
-        <v>15600</v>
-      </c>
       <c r="H61" s="3">
-        <v>16300</v>
+        <v>15700</v>
       </c>
       <c r="I61" s="3">
-        <v>16800</v>
+        <v>16500</v>
       </c>
       <c r="J61" s="3">
+        <v>17000</v>
+      </c>
+      <c r="K61" s="3">
         <v>17200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>11800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>10700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>12100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>11100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>23200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>32400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>34700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>36200</v>
-      </c>
-      <c r="U61" s="3">
-        <v>52000</v>
       </c>
       <c r="V61" s="3">
         <v>52000</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>52000</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>44600</v>
+        <v>46000</v>
       </c>
       <c r="E62" s="3">
-        <v>46200</v>
+        <v>45100</v>
       </c>
       <c r="F62" s="3">
-        <v>48100</v>
+        <v>46600</v>
       </c>
       <c r="G62" s="3">
-        <v>48900</v>
+        <v>48600</v>
       </c>
       <c r="H62" s="3">
-        <v>50600</v>
+        <v>49400</v>
       </c>
       <c r="I62" s="3">
-        <v>49700</v>
+        <v>51100</v>
       </c>
       <c r="J62" s="3">
+        <v>50200</v>
+      </c>
+      <c r="K62" s="3">
         <v>51200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>54000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>54700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>9700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>6900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3839,8 +3988,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3901,8 +4053,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3963,70 +4118,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>145300</v>
+        <v>153400</v>
       </c>
       <c r="E66" s="3">
-        <v>144000</v>
+        <v>146700</v>
       </c>
       <c r="F66" s="3">
-        <v>132900</v>
+        <v>145400</v>
       </c>
       <c r="G66" s="3">
-        <v>129300</v>
+        <v>134300</v>
       </c>
       <c r="H66" s="3">
-        <v>142400</v>
+        <v>130600</v>
       </c>
       <c r="I66" s="3">
-        <v>148000</v>
+        <v>143800</v>
       </c>
       <c r="J66" s="3">
+        <v>149500</v>
+      </c>
+      <c r="K66" s="3">
         <v>149600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>150700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>148900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>90100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>81500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>68500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>154800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>126400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>133400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>130400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>134600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>177400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>188700</v>
       </c>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4049,8 +4210,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4111,8 +4273,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4173,8 +4338,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4235,8 +4403,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4297,70 +4468,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-89200</v>
+        <v>-92400</v>
       </c>
       <c r="E72" s="3">
-        <v>-88100</v>
+        <v>-90000</v>
       </c>
       <c r="F72" s="3">
-        <v>-84100</v>
+        <v>-89000</v>
       </c>
       <c r="G72" s="3">
-        <v>-82700</v>
+        <v>-85000</v>
       </c>
       <c r="H72" s="3">
-        <v>-82900</v>
+        <v>-83500</v>
       </c>
       <c r="I72" s="3">
-        <v>-83600</v>
+        <v>-83700</v>
       </c>
       <c r="J72" s="3">
+        <v>-84400</v>
+      </c>
+      <c r="K72" s="3">
         <v>-81400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-79100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-74600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-73900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-69500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-62200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-64900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-56300</v>
-      </c>
-      <c r="R72" s="3">
-        <v>-58700</v>
       </c>
       <c r="S72" s="3">
         <v>-58700</v>
       </c>
       <c r="T72" s="3">
+        <v>-58700</v>
+      </c>
+      <c r="U72" s="3">
         <v>-62100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-84300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-79700</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4421,8 +4598,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4483,8 +4663,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4545,70 +4728,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-1000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>10300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>16700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>25300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>5700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>9600</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4669,137 +4858,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E80" s="2">
         <v>45192</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45010</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44828</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44646</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44464</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44282</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43918</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>43736</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>43554</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>43372</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43190</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43001</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>42819</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>42637</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>42455</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>42273</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>42091</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>41909</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>4</v>
+      <c r="D81" s="3">
+        <v>-2300</v>
       </c>
       <c r="E81" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F81" s="3">
         <v>-4000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-6000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-3400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-5900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-8300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>15300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>5300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>3400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-4600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4822,70 +5020,74 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>4</v>
+      <c r="D83" s="3">
+        <v>2600</v>
       </c>
       <c r="E83" s="3">
-        <v>4100</v>
+        <v>2300</v>
       </c>
       <c r="F83" s="3">
-        <v>-2300</v>
+        <v>2200</v>
       </c>
       <c r="G83" s="3">
-        <v>4200</v>
+        <v>1900</v>
       </c>
       <c r="H83" s="3">
-        <v>-1600</v>
+        <v>1800</v>
       </c>
       <c r="I83" s="3">
-        <v>4000</v>
+        <v>2400</v>
       </c>
       <c r="J83" s="3">
+        <v>1900</v>
+      </c>
+      <c r="K83" s="3">
         <v>-1500</v>
-      </c>
-      <c r="K83" s="3">
-        <v>1800</v>
       </c>
       <c r="L83" s="3">
         <v>1800</v>
       </c>
       <c r="M83" s="3">
+        <v>1800</v>
+      </c>
+      <c r="N83" s="3">
         <v>1500</v>
       </c>
-      <c r="N83" s="3" t="s">
+      <c r="O83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1800</v>
-      </c>
-      <c r="R83" s="3">
-        <v>2000</v>
       </c>
       <c r="S83" s="3">
         <v>2000</v>
       </c>
       <c r="T83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="U83" s="3">
         <v>1900</v>
-      </c>
-      <c r="U83" s="3">
-        <v>3000</v>
       </c>
       <c r="V83" s="3">
         <v>3000</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4946,8 +5148,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5008,8 +5213,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5070,8 +5278,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5132,8 +5343,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5194,70 +5408,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
+      <c r="D89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>300</v>
+      </c>
+      <c r="F89" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="G89" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="H89" s="3">
+        <v>6800</v>
+      </c>
+      <c r="I89" s="3">
+        <v>6900</v>
+      </c>
+      <c r="J89" s="3">
+        <v>5300</v>
+      </c>
+      <c r="K89" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="L89" s="3">
+        <v>1400</v>
+      </c>
+      <c r="M89" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="N89" s="3">
+        <v>1700</v>
+      </c>
+      <c r="O89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E89" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-17100</v>
-      </c>
-      <c r="G89" s="3">
-        <v>13600</v>
-      </c>
-      <c r="H89" s="3">
-        <v>8100</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="K89" s="3">
-        <v>1400</v>
-      </c>
-      <c r="L89" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="M89" s="3">
-        <v>1700</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-13200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-10200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>7300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>9300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-5800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>8500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5280,70 +5500,74 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="F91" s="3">
         <v>-4500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-4900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-2900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-2900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-2000</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-2400</v>
       </c>
       <c r="K91" s="3">
         <v>-2400</v>
       </c>
       <c r="L91" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="M91" s="3">
         <v>-4000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3800</v>
       </c>
-      <c r="N91" s="3" t="s">
+      <c r="O91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1100</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-2400</v>
       </c>
       <c r="U91" s="3">
         <v>-2400</v>
       </c>
       <c r="V91" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="W91" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5404,8 +5628,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5466,70 +5693,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
+      <c r="D94" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="K94" s="3">
+        <v>3900</v>
+      </c>
+      <c r="L94" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="M94" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="N94" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="O94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E94" s="3">
-        <v>-6900</v>
-      </c>
-      <c r="F94" s="3">
+      <c r="P94" s="3">
+        <v>102500</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="R94" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="S94" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="T94" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="U94" s="3">
         <v>600</v>
       </c>
-      <c r="G94" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="H94" s="3">
-        <v>100</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="J94" s="3">
-        <v>3900</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O94" s="3">
-        <v>102500</v>
-      </c>
-      <c r="P94" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="R94" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="S94" s="3">
+      <c r="V94" s="3">
         <v>-2400</v>
       </c>
-      <c r="T94" s="3">
-        <v>600</v>
-      </c>
-      <c r="U94" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5552,8 +5785,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5614,8 +5848,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5676,8 +5913,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5738,8 +5978,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5800,70 +6043,76 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
+      <c r="D100" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F100" s="3">
+        <v>4600</v>
+      </c>
+      <c r="G100" s="3">
+        <v>6800</v>
+      </c>
+      <c r="H100" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="K100" s="3">
+        <v>1200</v>
+      </c>
+      <c r="L100" s="3">
+        <v>-400</v>
+      </c>
+      <c r="M100" s="3">
+        <v>7900</v>
+      </c>
+      <c r="N100" s="3">
+        <v>1800</v>
+      </c>
+      <c r="O100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E100" s="3">
-        <v>11400</v>
-      </c>
-      <c r="F100" s="3">
-        <v>16000</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-9200</v>
-      </c>
-      <c r="H100" s="3">
-        <v>-8400</v>
-      </c>
-      <c r="I100" s="3">
-        <v>4300</v>
-      </c>
-      <c r="J100" s="3">
-        <v>1200</v>
-      </c>
-      <c r="K100" s="3">
-        <v>-400</v>
-      </c>
-      <c r="L100" s="3">
-        <v>7900</v>
-      </c>
-      <c r="M100" s="3">
-        <v>1800</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-72700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>18800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-7300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>5100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-8000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>6400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-6500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5901,89 +6150,95 @@
         <v>0</v>
       </c>
       <c r="O101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P101" s="3">
         <v>-100</v>
       </c>
       <c r="Q101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
       </c>
       <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
         <v>-100</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
       <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
         <v>-200</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
+      <c r="D102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>500</v>
+      </c>
+      <c r="F102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H102" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I102" s="3">
+        <v>600</v>
+      </c>
+      <c r="J102" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K102" s="3">
+        <v>1800</v>
+      </c>
+      <c r="L102" s="3">
+        <v>-700</v>
+      </c>
+      <c r="M102" s="3">
+        <v>300</v>
+      </c>
+      <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E102" s="3">
-        <v>-500</v>
-      </c>
-      <c r="F102" s="3">
-        <v>-500</v>
-      </c>
-      <c r="G102" s="3">
-        <v>200</v>
-      </c>
-      <c r="H102" s="3">
-        <v>-300</v>
-      </c>
-      <c r="I102" s="3">
-        <v>900</v>
-      </c>
-      <c r="J102" s="3">
-        <v>1800</v>
-      </c>
-      <c r="K102" s="3">
-        <v>-700</v>
-      </c>
-      <c r="L102" s="3">
-        <v>300</v>
-      </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BGI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BGI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="92">
   <si>
     <t>BGI</t>
   </si>
@@ -656,18 +656,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -682,280 +681,306 @@
     <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45471</v>
+      </c>
+      <c r="F7" s="2">
         <v>45381</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
+        <v>45290</v>
+      </c>
+      <c r="H7" s="2">
         <v>45192</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
+        <v>45100</v>
+      </c>
+      <c r="J7" s="2">
         <v>45010</v>
       </c>
-      <c r="G7" s="2">
-        <v>44828</v>
-      </c>
-      <c r="H7" s="2">
-        <v>44646</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44464</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44282</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>43918</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>43736</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43554</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43372</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43190</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43001</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>42819</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>42637</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>42455</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>42273</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>42091</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>41909</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>71800</v>
+        <v>29700</v>
       </c>
       <c r="E8" s="3">
-        <v>64600</v>
+        <v>29300</v>
       </c>
       <c r="F8" s="3">
-        <v>61000</v>
+        <v>36000</v>
       </c>
       <c r="G8" s="3">
-        <v>58900</v>
+        <v>36900</v>
       </c>
       <c r="H8" s="3">
-        <v>71200</v>
+        <v>32600</v>
       </c>
       <c r="I8" s="3">
+        <v>33200</v>
+      </c>
+      <c r="J8" s="3">
+        <v>30100</v>
+      </c>
+      <c r="K8" s="3">
         <v>62300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>63300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>41500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>61100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>63200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>61800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>52700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>63500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>54000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>46900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>39900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>113000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>99700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>161900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>139700</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>44100</v>
+        <v>18100</v>
       </c>
       <c r="E9" s="3">
-        <v>38100</v>
+        <v>17800</v>
       </c>
       <c r="F9" s="3">
-        <v>35900</v>
+        <v>22100</v>
       </c>
       <c r="G9" s="3">
-        <v>34000</v>
+        <v>22700</v>
       </c>
       <c r="H9" s="3">
-        <v>40800</v>
+        <v>19200</v>
       </c>
       <c r="I9" s="3">
+        <v>19600</v>
+      </c>
+      <c r="J9" s="3">
+        <v>17800</v>
+      </c>
+      <c r="K9" s="3">
         <v>36600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>38700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>24900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>38000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>39100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>37600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>32500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>40500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>32300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>28400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>23500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>70000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>61300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>99500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>84300</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>27600</v>
+        <v>11600</v>
       </c>
       <c r="E10" s="3">
-        <v>26500</v>
+        <v>11400</v>
       </c>
       <c r="F10" s="3">
-        <v>25100</v>
+        <v>13800</v>
       </c>
       <c r="G10" s="3">
-        <v>24900</v>
+        <v>14200</v>
       </c>
       <c r="H10" s="3">
-        <v>30400</v>
+        <v>13400</v>
       </c>
       <c r="I10" s="3">
+        <v>13700</v>
+      </c>
+      <c r="J10" s="3">
+        <v>12400</v>
+      </c>
+      <c r="K10" s="3">
         <v>25700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>24600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>16600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>23200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>24100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>24200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>20200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>23100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>21600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>18500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>16400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>43000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>38400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>62400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>55400</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -979,8 +1004,10 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1044,8 +1071,14 @@
       <c r="W12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1109,8 +1142,14 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1132,115 +1171,127 @@
       <c r="I14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N14" s="3">
         <v>200</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>2900</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>500</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>5500</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2600</v>
+        <v>1400</v>
       </c>
       <c r="E15" s="3">
-        <v>2300</v>
+        <v>1400</v>
       </c>
       <c r="F15" s="3">
-        <v>2200</v>
+        <v>1300</v>
       </c>
       <c r="G15" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H15" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I15" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J15" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K15" s="3">
+        <v>2400</v>
+      </c>
+      <c r="L15" s="3">
         <v>1900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="M15" s="3">
+        <v>2100</v>
+      </c>
+      <c r="N15" s="3">
         <v>1800</v>
       </c>
-      <c r="I15" s="3">
-        <v>2400</v>
-      </c>
-      <c r="J15" s="3">
+      <c r="O15" s="3">
+        <v>1800</v>
+      </c>
+      <c r="P15" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>1500</v>
+      </c>
+      <c r="R15" s="3">
+        <v>1300</v>
+      </c>
+      <c r="S15" s="3">
+        <v>1400</v>
+      </c>
+      <c r="T15" s="3">
+        <v>900</v>
+      </c>
+      <c r="U15" s="3">
+        <v>1100</v>
+      </c>
+      <c r="V15" s="3">
+        <v>2000</v>
+      </c>
+      <c r="W15" s="3">
         <v>1900</v>
       </c>
-      <c r="K15" s="3">
-        <v>2100</v>
-      </c>
-      <c r="L15" s="3">
-        <v>1800</v>
-      </c>
-      <c r="M15" s="3">
-        <v>1800</v>
-      </c>
-      <c r="N15" s="3">
-        <v>1500</v>
-      </c>
-      <c r="O15" s="3">
-        <v>1500</v>
-      </c>
-      <c r="P15" s="3">
-        <v>1300</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>1400</v>
-      </c>
-      <c r="R15" s="3">
-        <v>900</v>
-      </c>
-      <c r="S15" s="3">
-        <v>1100</v>
-      </c>
-      <c r="T15" s="3">
-        <v>2000</v>
-      </c>
-      <c r="U15" s="3">
-        <v>1900</v>
-      </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>2900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1261,138 +1312,152 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>71200</v>
+        <v>29800</v>
       </c>
       <c r="E17" s="3">
-        <v>64300</v>
+        <v>29400</v>
       </c>
       <c r="F17" s="3">
-        <v>63300</v>
+        <v>35700</v>
       </c>
       <c r="G17" s="3">
-        <v>59400</v>
+        <v>36600</v>
       </c>
       <c r="H17" s="3">
-        <v>69900</v>
+        <v>32400</v>
       </c>
       <c r="I17" s="3">
+        <v>33100</v>
+      </c>
+      <c r="J17" s="3">
+        <v>31300</v>
+      </c>
+      <c r="K17" s="3">
         <v>60300</v>
-      </c>
-      <c r="J17" s="3">
-        <v>64400</v>
-      </c>
-      <c r="K17" s="3">
-        <v>42600</v>
       </c>
       <c r="L17" s="3">
         <v>64400</v>
       </c>
       <c r="M17" s="3">
+        <v>42600</v>
+      </c>
+      <c r="N17" s="3">
+        <v>64400</v>
+      </c>
+      <c r="O17" s="3">
         <v>64700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>65700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>59200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>73000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>58800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>48100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>41300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>106000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>95200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>161900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>137000</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>600</v>
+        <v>-100</v>
       </c>
       <c r="E18" s="3">
-        <v>400</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="3">
-        <v>-2300</v>
+        <v>300</v>
       </c>
       <c r="G18" s="3">
-        <v>-500</v>
+        <v>300</v>
       </c>
       <c r="H18" s="3">
-        <v>1300</v>
+        <v>200</v>
       </c>
       <c r="I18" s="3">
-        <v>2000</v>
+        <v>200</v>
       </c>
       <c r="J18" s="3">
         <v>-1100</v>
       </c>
       <c r="K18" s="3">
+        <v>2000</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="M18" s="3">
         <v>-1000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-3200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-1600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-3900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-6500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-4900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-1300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-1400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>7000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>4500</v>
       </c>
-      <c r="V18" s="3">
-        <v>0</v>
-      </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1416,31 +1481,33 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>600</v>
+        <v>-500</v>
       </c>
       <c r="E20" s="3">
-        <v>1000</v>
+        <v>-400</v>
       </c>
       <c r="F20" s="3">
-        <v>800</v>
+        <v>-400</v>
       </c>
       <c r="G20" s="3">
-        <v>700</v>
+        <v>-400</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1481,226 +1548,250 @@
       <c r="W20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>3700</v>
+        <v>1700</v>
       </c>
       <c r="E21" s="3">
-        <v>3700</v>
+        <v>1700</v>
       </c>
       <c r="F21" s="3">
-        <v>700</v>
+        <v>1900</v>
       </c>
       <c r="G21" s="3">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="H21" s="3">
-        <v>3200</v>
+        <v>1800</v>
       </c>
       <c r="I21" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J21" s="3">
+        <v>200</v>
+      </c>
+      <c r="K21" s="3">
         <v>4400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-2500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-1500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-2400</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R21" s="3">
         <v>-8200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-3500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>7200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>6400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>2900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>3400</v>
+        <v>1500</v>
       </c>
       <c r="E22" s="3">
-        <v>2500</v>
+        <v>1500</v>
       </c>
       <c r="F22" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G22" s="3">
+        <v>1800</v>
+      </c>
+      <c r="H22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="L22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="M22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N22" s="3">
         <v>2400</v>
       </c>
-      <c r="G22" s="3">
-        <v>1700</v>
-      </c>
-      <c r="H22" s="3">
-        <v>1100</v>
-      </c>
-      <c r="I22" s="3">
+      <c r="O22" s="3">
+        <v>1800</v>
+      </c>
+      <c r="P22" s="3">
+        <v>2100</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="R22" s="3">
+        <v>2000</v>
+      </c>
+      <c r="S22" s="3">
         <v>1200</v>
       </c>
-      <c r="J22" s="3">
-        <v>1200</v>
-      </c>
-      <c r="K22" s="3">
+      <c r="T22" s="3">
         <v>1000</v>
       </c>
-      <c r="L22" s="3">
-        <v>2400</v>
-      </c>
-      <c r="M22" s="3">
-        <v>1800</v>
-      </c>
-      <c r="N22" s="3">
-        <v>2100</v>
-      </c>
-      <c r="O22" s="3">
-        <v>1400</v>
-      </c>
-      <c r="P22" s="3">
-        <v>2000</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>1200</v>
-      </c>
-      <c r="R22" s="3">
-        <v>1000</v>
-      </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>1500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>3600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>3900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>4600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-2300</v>
+        <v>-1100</v>
       </c>
       <c r="E23" s="3">
         <v>-1100</v>
       </c>
       <c r="F23" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="G23" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-600</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="K23" s="3">
+        <v>700</v>
+      </c>
+      <c r="L23" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="M23" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="N23" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="O23" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="P23" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="R23" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="S23" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="T23" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="U23" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="V23" s="3">
+        <v>3400</v>
+      </c>
+      <c r="W23" s="3">
+        <v>700</v>
+      </c>
+      <c r="X23" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="Y23" s="3">
         <v>-4000</v>
       </c>
-      <c r="G23" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="H23" s="3">
-        <v>200</v>
-      </c>
-      <c r="I23" s="3">
-        <v>700</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-5600</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="N23" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="O23" s="3">
-        <v>-7900</v>
-      </c>
-      <c r="P23" s="3">
-        <v>-11400</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>-6100</v>
-      </c>
-      <c r="R23" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="S23" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="T23" s="3">
-        <v>3400</v>
-      </c>
-      <c r="U23" s="3">
-        <v>700</v>
-      </c>
-      <c r="V23" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="W23" s="3">
-        <v>-4000</v>
-      </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1741,8 +1832,14 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1806,138 +1903,156 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-2300</v>
+        <v>-1100</v>
       </c>
       <c r="E26" s="3">
         <v>-1100</v>
       </c>
       <c r="F26" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="G26" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-600</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="K26" s="3">
+        <v>700</v>
+      </c>
+      <c r="L26" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="M26" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="N26" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="O26" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="P26" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="R26" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="S26" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="T26" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="U26" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="V26" s="3">
+        <v>3400</v>
+      </c>
+      <c r="W26" s="3">
+        <v>600</v>
+      </c>
+      <c r="X26" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="Y26" s="3">
         <v>-4000</v>
       </c>
-      <c r="G26" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="H26" s="3">
-        <v>200</v>
-      </c>
-      <c r="I26" s="3">
-        <v>700</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-5600</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="N26" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="O26" s="3">
-        <v>-7900</v>
-      </c>
-      <c r="P26" s="3">
-        <v>-11400</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>-6100</v>
-      </c>
-      <c r="R26" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="S26" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="T26" s="3">
-        <v>3400</v>
-      </c>
-      <c r="U26" s="3">
-        <v>600</v>
-      </c>
-      <c r="V26" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="W26" s="3">
-        <v>-4000</v>
-      </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-2300</v>
+        <v>-1100</v>
       </c>
       <c r="E27" s="3">
         <v>-1100</v>
       </c>
       <c r="F27" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="G27" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-600</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="K27" s="3">
+        <v>700</v>
+      </c>
+      <c r="L27" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="M27" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="N27" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="O27" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="P27" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="R27" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="S27" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="T27" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="U27" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="V27" s="3">
+        <v>3400</v>
+      </c>
+      <c r="W27" s="3">
+        <v>600</v>
+      </c>
+      <c r="X27" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="Y27" s="3">
         <v>-4000</v>
       </c>
-      <c r="G27" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="H27" s="3">
-        <v>200</v>
-      </c>
-      <c r="I27" s="3">
-        <v>700</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="L27" s="3">
-        <v>-5600</v>
-      </c>
-      <c r="M27" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="N27" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="O27" s="3">
-        <v>-7900</v>
-      </c>
-      <c r="P27" s="3">
-        <v>-11400</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>-6100</v>
-      </c>
-      <c r="R27" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="S27" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="T27" s="3">
-        <v>3400</v>
-      </c>
-      <c r="U27" s="3">
-        <v>600</v>
-      </c>
-      <c r="V27" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="W27" s="3">
-        <v>-4000</v>
-      </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2001,73 +2116,85 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>4</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
+      <c r="K29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>-300</v>
       </c>
-      <c r="M29" s="3">
+      <c r="O29" s="3">
         <v>-100</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>-300</v>
       </c>
-      <c r="P29" s="3">
+      <c r="R29" s="3">
         <v>26700</v>
-      </c>
-      <c r="Q29" s="3">
-        <v>1500</v>
-      </c>
-      <c r="R29" s="3">
-        <v>7600</v>
       </c>
       <c r="S29" s="3">
         <v>1500</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>7600</v>
+      </c>
+      <c r="U29" s="3">
+        <v>1500</v>
+      </c>
+      <c r="V29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2131,8 +2258,14 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2196,31 +2329,37 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-600</v>
+        <v>500</v>
       </c>
       <c r="E32" s="3">
-        <v>-1000</v>
+        <v>400</v>
       </c>
       <c r="F32" s="3">
-        <v>-800</v>
+        <v>400</v>
       </c>
       <c r="G32" s="3">
-        <v>-700</v>
+        <v>400</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -2261,73 +2400,85 @@
       <c r="W32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-2300</v>
+        <v>-1100</v>
       </c>
       <c r="E33" s="3">
         <v>-1100</v>
       </c>
       <c r="F33" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="G33" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-600</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="K33" s="3">
+        <v>700</v>
+      </c>
+      <c r="L33" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="M33" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="N33" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="O33" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="P33" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="R33" s="3">
+        <v>15300</v>
+      </c>
+      <c r="S33" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="T33" s="3">
+        <v>5300</v>
+      </c>
+      <c r="U33" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="V33" s="3">
+        <v>3400</v>
+      </c>
+      <c r="W33" s="3">
+        <v>600</v>
+      </c>
+      <c r="X33" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="Y33" s="3">
         <v>-4000</v>
       </c>
-      <c r="G33" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="H33" s="3">
-        <v>200</v>
-      </c>
-      <c r="I33" s="3">
-        <v>700</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="L33" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="M33" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="N33" s="3">
-        <v>-5900</v>
-      </c>
-      <c r="O33" s="3">
-        <v>-8300</v>
-      </c>
-      <c r="P33" s="3">
-        <v>15300</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="R33" s="3">
-        <v>5300</v>
-      </c>
-      <c r="S33" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="T33" s="3">
-        <v>3400</v>
-      </c>
-      <c r="U33" s="3">
-        <v>600</v>
-      </c>
-      <c r="V33" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="W33" s="3">
-        <v>-4000</v>
-      </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2391,143 +2542,161 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-2300</v>
+        <v>-1100</v>
       </c>
       <c r="E35" s="3">
         <v>-1100</v>
       </c>
       <c r="F35" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="G35" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-600</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="K35" s="3">
+        <v>700</v>
+      </c>
+      <c r="L35" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="M35" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="N35" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="O35" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="P35" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="R35" s="3">
+        <v>15300</v>
+      </c>
+      <c r="S35" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="T35" s="3">
+        <v>5300</v>
+      </c>
+      <c r="U35" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="V35" s="3">
+        <v>3400</v>
+      </c>
+      <c r="W35" s="3">
+        <v>600</v>
+      </c>
+      <c r="X35" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="Y35" s="3">
         <v>-4000</v>
       </c>
-      <c r="G35" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="H35" s="3">
-        <v>200</v>
-      </c>
-      <c r="I35" s="3">
-        <v>700</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="L35" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="M35" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="N35" s="3">
-        <v>-5900</v>
-      </c>
-      <c r="O35" s="3">
-        <v>-8300</v>
-      </c>
-      <c r="P35" s="3">
-        <v>15300</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="R35" s="3">
-        <v>5300</v>
-      </c>
-      <c r="S35" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="T35" s="3">
-        <v>3400</v>
-      </c>
-      <c r="U35" s="3">
-        <v>600</v>
-      </c>
-      <c r="V35" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="W35" s="3">
-        <v>-4000</v>
-      </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45471</v>
+      </c>
+      <c r="F38" s="2">
         <v>45381</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
+        <v>45290</v>
+      </c>
+      <c r="H38" s="2">
         <v>45192</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
+        <v>45100</v>
+      </c>
+      <c r="J38" s="2">
         <v>45010</v>
       </c>
-      <c r="G38" s="2">
-        <v>44828</v>
-      </c>
-      <c r="H38" s="2">
-        <v>44646</v>
-      </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44464</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44282</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>43918</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>43736</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43554</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43372</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43190</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43001</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>42819</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>42637</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>42455</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>42273</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>42091</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>41909</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2551,8 +2720,10 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2576,8 +2747,10 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2585,64 +2758,70 @@
         <v>1300</v>
       </c>
       <c r="E41" s="3">
-        <v>1500</v>
+        <v>1300</v>
       </c>
       <c r="F41" s="3">
-        <v>900</v>
+        <v>1300</v>
       </c>
       <c r="G41" s="3">
-        <v>1200</v>
+        <v>1400</v>
       </c>
       <c r="H41" s="3">
         <v>1500</v>
       </c>
       <c r="I41" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J41" s="3">
+        <v>900</v>
+      </c>
+      <c r="K41" s="3">
         <v>2000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>2100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>1500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>2800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>1700</v>
-      </c>
-      <c r="U41" s="3">
-        <v>3000</v>
-      </c>
-      <c r="V41" s="3">
-        <v>2400</v>
       </c>
       <c r="W41" s="3">
         <v>3000</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3">
+        <v>2400</v>
+      </c>
+      <c r="Y41" s="3">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2706,164 +2885,182 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>5100</v>
+      </c>
+      <c r="F43" s="3">
         <v>6200</v>
       </c>
-      <c r="E43" s="3">
-        <v>6600</v>
-      </c>
-      <c r="F43" s="3">
-        <v>8400</v>
-      </c>
       <c r="G43" s="3">
-        <v>8900</v>
+        <v>6400</v>
       </c>
       <c r="H43" s="3">
-        <v>5900</v>
+        <v>6700</v>
       </c>
       <c r="I43" s="3">
+        <v>6800</v>
+      </c>
+      <c r="J43" s="3">
+        <v>8300</v>
+      </c>
+      <c r="K43" s="3">
         <v>6000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>5400</v>
-      </c>
-      <c r="K43" s="3">
-        <v>4600</v>
-      </c>
-      <c r="L43" s="3">
-        <v>4400</v>
       </c>
       <c r="M43" s="3">
         <v>4600</v>
       </c>
       <c r="N43" s="3">
+        <v>4400</v>
+      </c>
+      <c r="O43" s="3">
+        <v>4600</v>
+      </c>
+      <c r="P43" s="3">
         <v>2700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>3100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>4800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>3700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>10300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>7300</v>
-      </c>
-      <c r="T43" s="3">
-        <v>7700</v>
-      </c>
-      <c r="U43" s="3">
-        <v>6800</v>
       </c>
       <c r="V43" s="3">
         <v>7700</v>
       </c>
       <c r="W43" s="3">
+        <v>6800</v>
+      </c>
+      <c r="X43" s="3">
+        <v>7700</v>
+      </c>
+      <c r="Y43" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>72900</v>
+        <v>78300</v>
       </c>
       <c r="E44" s="3">
-        <v>67700</v>
+        <v>77200</v>
       </c>
       <c r="F44" s="3">
-        <v>65000</v>
+        <v>73200</v>
       </c>
       <c r="G44" s="3">
-        <v>57300</v>
+        <v>75000</v>
       </c>
       <c r="H44" s="3">
-        <v>58100</v>
+        <v>68400</v>
       </c>
       <c r="I44" s="3">
+        <v>69700</v>
+      </c>
+      <c r="J44" s="3">
+        <v>64300</v>
+      </c>
+      <c r="K44" s="3">
         <v>65200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>72000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>73100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>74100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>75300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>68700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>67900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>66100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>59700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>100500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>103800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>102600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>101300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>135700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>150400</v>
       </c>
     </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>2100</v>
-      </c>
-      <c r="E45" s="3">
-        <v>2000</v>
-      </c>
-      <c r="F45" s="3">
-        <v>2000</v>
-      </c>
-      <c r="G45" s="3">
-        <v>2000</v>
-      </c>
-      <c r="H45" s="3">
-        <v>1300</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K45" s="3">
         <v>1600</v>
-      </c>
-      <c r="J45" s="3">
-        <v>1500</v>
-      </c>
-      <c r="K45" s="3">
-        <v>1500</v>
       </c>
       <c r="L45" s="3">
         <v>1500</v>
@@ -2872,149 +3069,161 @@
         <v>1500</v>
       </c>
       <c r="N45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="O45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="P45" s="3">
         <v>1600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>2600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>3800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>82200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>1700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>1600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>1300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>1400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>2200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>82600</v>
+        <v>86800</v>
       </c>
       <c r="E46" s="3">
-        <v>77900</v>
+        <v>85600</v>
       </c>
       <c r="F46" s="3">
-        <v>76300</v>
+        <v>82900</v>
       </c>
       <c r="G46" s="3">
-        <v>69400</v>
+        <v>85000</v>
       </c>
       <c r="H46" s="3">
-        <v>66800</v>
+        <v>78600</v>
       </c>
       <c r="I46" s="3">
+        <v>80100</v>
+      </c>
+      <c r="J46" s="3">
+        <v>75400</v>
+      </c>
+      <c r="K46" s="3">
         <v>74700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>80200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>80900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>80300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>82500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>73900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>74500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>75600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>147700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>114000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>115600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>113300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>112500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>148000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>162600</v>
       </c>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F47" s="3">
+        <v>3000</v>
+      </c>
+      <c r="G47" s="3">
+        <v>3100</v>
+      </c>
+      <c r="H47" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I47" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J47" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K47" s="3">
         <v>4200</v>
       </c>
-      <c r="E47" s="3">
-        <v>3600</v>
-      </c>
-      <c r="F47" s="3">
+      <c r="L47" s="3">
+        <v>4200</v>
+      </c>
+      <c r="M47" s="3">
+        <v>3400</v>
+      </c>
+      <c r="N47" s="3">
+        <v>3300</v>
+      </c>
+      <c r="O47" s="3">
         <v>2900</v>
       </c>
-      <c r="G47" s="3">
-        <v>3400</v>
-      </c>
-      <c r="H47" s="3">
-        <v>4100</v>
-      </c>
-      <c r="I47" s="3">
-        <v>4200</v>
-      </c>
-      <c r="J47" s="3">
-        <v>4200</v>
-      </c>
-      <c r="K47" s="3">
-        <v>3400</v>
-      </c>
-      <c r="L47" s="3">
-        <v>3300</v>
-      </c>
-      <c r="M47" s="3">
-        <v>2900</v>
-      </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>1000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>700</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R47" s="3" t="s">
-        <v>4</v>
+      <c r="R47" s="3">
+        <v>0</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>4</v>
@@ -3025,144 +3234,162 @@
       <c r="U47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V47" s="3">
-        <v>0</v>
-      </c>
-      <c r="W47" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>57000</v>
+        <v>45300</v>
       </c>
       <c r="E48" s="3">
-        <v>58200</v>
+        <v>44600</v>
       </c>
       <c r="F48" s="3">
-        <v>60600</v>
+        <v>57200</v>
       </c>
       <c r="G48" s="3">
-        <v>60400</v>
+        <v>58700</v>
       </c>
       <c r="H48" s="3">
-        <v>59500</v>
+        <v>58700</v>
       </c>
       <c r="I48" s="3">
+        <v>59900</v>
+      </c>
+      <c r="J48" s="3">
+        <v>59900</v>
+      </c>
+      <c r="K48" s="3">
         <v>60500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>60500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>62200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>65900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>68900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>22300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>18400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>15100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>11900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>17500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>21200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>21900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>22100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>28500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>31700</v>
       </c>
     </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>5900</v>
+      </c>
+      <c r="F49" s="3">
         <v>5800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
+        <v>6000</v>
+      </c>
+      <c r="H49" s="3">
         <v>5600</v>
       </c>
-      <c r="F49" s="3">
-        <v>5200</v>
-      </c>
-      <c r="G49" s="3">
-        <v>4400</v>
-      </c>
-      <c r="H49" s="3">
-        <v>4400</v>
-      </c>
       <c r="I49" s="3">
+        <v>5700</v>
+      </c>
+      <c r="J49" s="3">
+        <v>5100</v>
+      </c>
+      <c r="K49" s="3">
         <v>4100</v>
-      </c>
-      <c r="J49" s="3">
-        <v>3600</v>
-      </c>
-      <c r="K49" s="3">
-        <v>3600</v>
       </c>
       <c r="L49" s="3">
         <v>3600</v>
       </c>
       <c r="M49" s="3">
+        <v>3600</v>
+      </c>
+      <c r="N49" s="3">
+        <v>3600</v>
+      </c>
+      <c r="O49" s="3">
         <v>3200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>3300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>4500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>3000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>2800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3226,8 +3453,14 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3291,31 +3524,37 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -3339,25 +3578,31 @@
         <v>0</v>
       </c>
       <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+      <c r="T52" s="3">
         <v>4200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>1600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>2700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3421,73 +3666,85 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>149600</v>
+        <v>143100</v>
       </c>
       <c r="E54" s="3">
-        <v>145200</v>
+        <v>141000</v>
       </c>
       <c r="F54" s="3">
-        <v>145000</v>
+        <v>150100</v>
       </c>
       <c r="G54" s="3">
-        <v>137500</v>
+        <v>153900</v>
       </c>
       <c r="H54" s="3">
-        <v>134900</v>
+        <v>146500</v>
       </c>
       <c r="I54" s="3">
+        <v>149400</v>
+      </c>
+      <c r="J54" s="3">
+        <v>143200</v>
+      </c>
+      <c r="K54" s="3">
         <v>143500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>148500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>150100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>153100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>157600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>100500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>98200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>93800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>162300</v>
-      </c>
-      <c r="R54" s="3">
-        <v>136200</v>
-      </c>
-      <c r="S54" s="3">
-        <v>137700</v>
       </c>
       <c r="T54" s="3">
         <v>136200</v>
       </c>
       <c r="U54" s="3">
+        <v>137700</v>
+      </c>
+      <c r="V54" s="3">
+        <v>136200</v>
+      </c>
+      <c r="W54" s="3">
         <v>136800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>180200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>198300</v>
       </c>
     </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3511,8 +3768,10 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3536,398 +3795,436 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>31700</v>
+        <v>33500</v>
       </c>
       <c r="E57" s="3">
-        <v>28400</v>
+        <v>33100</v>
       </c>
       <c r="F57" s="3">
-        <v>27700</v>
+        <v>31800</v>
       </c>
       <c r="G57" s="3">
-        <v>19800</v>
+        <v>32600</v>
       </c>
       <c r="H57" s="3">
+        <v>28600</v>
+      </c>
+      <c r="I57" s="3">
+        <v>29200</v>
+      </c>
+      <c r="J57" s="3">
+        <v>27400</v>
+      </c>
+      <c r="K57" s="3">
+        <v>25500</v>
+      </c>
+      <c r="L57" s="3">
+        <v>28000</v>
+      </c>
+      <c r="M57" s="3">
+        <v>26300</v>
+      </c>
+      <c r="N57" s="3">
+        <v>35000</v>
+      </c>
+      <c r="O57" s="3">
+        <v>29700</v>
+      </c>
+      <c r="P57" s="3">
+        <v>25000</v>
+      </c>
+      <c r="Q57" s="3">
         <v>20800</v>
       </c>
-      <c r="I57" s="3">
-        <v>25500</v>
-      </c>
-      <c r="J57" s="3">
-        <v>28000</v>
-      </c>
-      <c r="K57" s="3">
-        <v>26300</v>
-      </c>
-      <c r="L57" s="3">
-        <v>35000</v>
-      </c>
-      <c r="M57" s="3">
-        <v>29700</v>
-      </c>
-      <c r="N57" s="3">
-        <v>25000</v>
-      </c>
-      <c r="O57" s="3">
-        <v>20800</v>
-      </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>20600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>19000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>35500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>35100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>34800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>31800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>44700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>46000</v>
       </c>
     </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>49900</v>
+        <v>62700</v>
       </c>
       <c r="E58" s="3">
-        <v>47000</v>
+        <v>61800</v>
       </c>
       <c r="F58" s="3">
-        <v>44200</v>
+        <v>54800</v>
       </c>
       <c r="G58" s="3">
-        <v>39600</v>
+        <v>56200</v>
       </c>
       <c r="H58" s="3">
-        <v>33300</v>
+        <v>52300</v>
       </c>
       <c r="I58" s="3">
+        <v>53300</v>
+      </c>
+      <c r="J58" s="3">
+        <v>48600</v>
+      </c>
+      <c r="K58" s="3">
         <v>37900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>41500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>45600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>42200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>44800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>36100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>36000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>31400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>46100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>55700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>56800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>50700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>58200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>69100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>79600</v>
       </c>
     </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>9200</v>
-      </c>
-      <c r="E59" s="3">
-        <v>9200</v>
-      </c>
-      <c r="F59" s="3">
-        <v>10600</v>
-      </c>
-      <c r="G59" s="3">
-        <v>10100</v>
-      </c>
-      <c r="H59" s="3">
-        <v>11300</v>
-      </c>
-      <c r="I59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K59" s="3">
         <v>12800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>12900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>9400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>7600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>8900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>7300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>6600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>5800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>79300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>6400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>5600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>6700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>5700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>8100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>90700</v>
+        <v>100700</v>
       </c>
       <c r="E60" s="3">
-        <v>84600</v>
+        <v>99300</v>
       </c>
       <c r="F60" s="3">
-        <v>82500</v>
+        <v>91000</v>
       </c>
       <c r="G60" s="3">
-        <v>69500</v>
+        <v>93300</v>
       </c>
       <c r="H60" s="3">
-        <v>65400</v>
+        <v>85300</v>
       </c>
       <c r="I60" s="3">
+        <v>87000</v>
+      </c>
+      <c r="J60" s="3">
+        <v>81500</v>
+      </c>
+      <c r="K60" s="3">
         <v>76200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>82300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>81300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>84900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>83500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>68300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>63400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>57800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>144500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>97600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>97500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>92200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>95700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>121900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>133400</v>
       </c>
     </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>16600</v>
+        <v>45300</v>
       </c>
       <c r="E61" s="3">
-        <v>17100</v>
+        <v>44700</v>
       </c>
       <c r="F61" s="3">
-        <v>16300</v>
+        <v>60900</v>
       </c>
       <c r="G61" s="3">
-        <v>16200</v>
+        <v>62400</v>
       </c>
       <c r="H61" s="3">
-        <v>15700</v>
+        <v>61500</v>
       </c>
       <c r="I61" s="3">
+        <v>62700</v>
+      </c>
+      <c r="J61" s="3">
+        <v>61900</v>
+      </c>
+      <c r="K61" s="3">
         <v>16500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>17000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>17200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>11800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>10700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>12100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>11100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>3800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>4400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>23200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>32400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>34700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>36200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>52000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>52000</v>
       </c>
     </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>46000</v>
+        <v>3200</v>
       </c>
       <c r="E62" s="3">
-        <v>45100</v>
+        <v>3100</v>
       </c>
       <c r="F62" s="3">
-        <v>46600</v>
+        <v>2000</v>
       </c>
       <c r="G62" s="3">
-        <v>48600</v>
+        <v>2000</v>
       </c>
       <c r="H62" s="3">
-        <v>49400</v>
+        <v>1300</v>
       </c>
       <c r="I62" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J62" s="3">
+        <v>300</v>
+      </c>
+      <c r="K62" s="3">
         <v>51100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>50200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>51200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>54000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>54700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>9700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>7000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>6900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>5900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>5600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>3500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>3600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>2700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>3400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3991,8 +4288,14 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4056,8 +4359,14 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4121,73 +4430,85 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>153400</v>
+        <v>149200</v>
       </c>
       <c r="E66" s="3">
-        <v>146700</v>
+        <v>147100</v>
       </c>
       <c r="F66" s="3">
-        <v>145400</v>
+        <v>153900</v>
       </c>
       <c r="G66" s="3">
-        <v>134300</v>
+        <v>157800</v>
       </c>
       <c r="H66" s="3">
-        <v>130600</v>
+        <v>148100</v>
       </c>
       <c r="I66" s="3">
+        <v>150900</v>
+      </c>
+      <c r="J66" s="3">
+        <v>143700</v>
+      </c>
+      <c r="K66" s="3">
         <v>143800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>149500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>149600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>150700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>148900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>90100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>81500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>68500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>154800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>126400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>133400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>130400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>134600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>177400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>188700</v>
       </c>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4211,8 +4532,10 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4276,8 +4599,14 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4341,8 +4670,14 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4406,8 +4741,14 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4471,73 +4812,85 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-92400</v>
+        <v>-95300</v>
       </c>
       <c r="E72" s="3">
-        <v>-90000</v>
+        <v>-93900</v>
       </c>
       <c r="F72" s="3">
-        <v>-89000</v>
+        <v>-92700</v>
       </c>
       <c r="G72" s="3">
-        <v>-85000</v>
+        <v>-95000</v>
       </c>
       <c r="H72" s="3">
-        <v>-83500</v>
+        <v>-90900</v>
       </c>
       <c r="I72" s="3">
+        <v>-92600</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-87900</v>
+      </c>
+      <c r="K72" s="3">
         <v>-83700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-84400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-81400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-79100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-74600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-73900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-69500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-62200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-64900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-56300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-58700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-58700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-62100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-84300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-79700</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4601,8 +4954,14 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4666,8 +5025,14 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4731,73 +5096,85 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="F76" s="3">
         <v>-3800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="H76" s="3">
         <v>-1500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="I76" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="J76" s="3">
         <v>-400</v>
       </c>
-      <c r="G76" s="3">
-        <v>3200</v>
-      </c>
-      <c r="H76" s="3">
+      <c r="K76" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L76" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="M76" s="3">
+        <v>500</v>
+      </c>
+      <c r="N76" s="3">
+        <v>2500</v>
+      </c>
+      <c r="O76" s="3">
+        <v>8600</v>
+      </c>
+      <c r="P76" s="3">
+        <v>10300</v>
+      </c>
+      <c r="Q76" s="3">
+        <v>16700</v>
+      </c>
+      <c r="R76" s="3">
+        <v>25300</v>
+      </c>
+      <c r="S76" s="3">
+        <v>7600</v>
+      </c>
+      <c r="T76" s="3">
+        <v>9700</v>
+      </c>
+      <c r="U76" s="3">
         <v>4300</v>
       </c>
-      <c r="I76" s="3">
-        <v>-300</v>
-      </c>
-      <c r="J76" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="K76" s="3">
-        <v>500</v>
-      </c>
-      <c r="L76" s="3">
-        <v>2500</v>
-      </c>
-      <c r="M76" s="3">
-        <v>8600</v>
-      </c>
-      <c r="N76" s="3">
-        <v>10300</v>
-      </c>
-      <c r="O76" s="3">
-        <v>16700</v>
-      </c>
-      <c r="P76" s="3">
-        <v>25300</v>
-      </c>
-      <c r="Q76" s="3">
-        <v>7600</v>
-      </c>
-      <c r="R76" s="3">
-        <v>9700</v>
-      </c>
-      <c r="S76" s="3">
-        <v>4300</v>
-      </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>5700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>2200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>2800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>9600</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4861,143 +5238,161 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45471</v>
+      </c>
+      <c r="F80" s="2">
         <v>45381</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
+        <v>45290</v>
+      </c>
+      <c r="H80" s="2">
         <v>45192</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
+        <v>45100</v>
+      </c>
+      <c r="J80" s="2">
         <v>45010</v>
       </c>
-      <c r="G80" s="2">
-        <v>44828</v>
-      </c>
-      <c r="H80" s="2">
-        <v>44646</v>
-      </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44464</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44282</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>43918</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>43736</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43554</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43372</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43190</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43001</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>42819</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>42637</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>42455</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>42273</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>42091</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>41909</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-2300</v>
+        <v>-1100</v>
       </c>
       <c r="E81" s="3">
         <v>-1100</v>
       </c>
       <c r="F81" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="G81" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-600</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="K81" s="3">
+        <v>700</v>
+      </c>
+      <c r="L81" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="M81" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="N81" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="O81" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="P81" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="Q81" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="R81" s="3">
+        <v>15300</v>
+      </c>
+      <c r="S81" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="T81" s="3">
+        <v>5300</v>
+      </c>
+      <c r="U81" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="V81" s="3">
+        <v>3400</v>
+      </c>
+      <c r="W81" s="3">
+        <v>600</v>
+      </c>
+      <c r="X81" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="Y81" s="3">
         <v>-4000</v>
       </c>
-      <c r="G81" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="H81" s="3">
-        <v>200</v>
-      </c>
-      <c r="I81" s="3">
-        <v>700</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="L81" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="M81" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="N81" s="3">
-        <v>-5900</v>
-      </c>
-      <c r="O81" s="3">
-        <v>-8300</v>
-      </c>
-      <c r="P81" s="3">
-        <v>15300</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="R81" s="3">
-        <v>5300</v>
-      </c>
-      <c r="S81" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="T81" s="3">
-        <v>3400</v>
-      </c>
-      <c r="U81" s="3">
-        <v>600</v>
-      </c>
-      <c r="V81" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="W81" s="3">
-        <v>-4000</v>
-      </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5021,73 +5416,81 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>2600</v>
+        <v>1200</v>
       </c>
       <c r="E83" s="3">
-        <v>2300</v>
+        <v>1200</v>
       </c>
       <c r="F83" s="3">
-        <v>2200</v>
+        <v>1100</v>
       </c>
       <c r="G83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K83" s="3">
+        <v>2400</v>
+      </c>
+      <c r="L83" s="3">
         <v>1900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="M83" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="N83" s="3">
         <v>1800</v>
       </c>
-      <c r="I83" s="3">
-        <v>2400</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="O83" s="3">
+        <v>1800</v>
+      </c>
+      <c r="P83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R83" s="3">
+        <v>1300</v>
+      </c>
+      <c r="S83" s="3">
+        <v>1400</v>
+      </c>
+      <c r="T83" s="3">
+        <v>1800</v>
+      </c>
+      <c r="U83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="V83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="W83" s="3">
         <v>1900</v>
       </c>
-      <c r="K83" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="L83" s="3">
-        <v>1800</v>
-      </c>
-      <c r="M83" s="3">
-        <v>1800</v>
-      </c>
-      <c r="N83" s="3">
-        <v>1500</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P83" s="3">
-        <v>1300</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>1400</v>
-      </c>
-      <c r="R83" s="3">
-        <v>1800</v>
-      </c>
-      <c r="S83" s="3">
-        <v>2000</v>
-      </c>
-      <c r="T83" s="3">
-        <v>2000</v>
-      </c>
-      <c r="U83" s="3">
-        <v>1900</v>
-      </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>3000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5151,8 +5554,14 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5216,8 +5625,14 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5281,8 +5696,14 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5346,8 +5767,14 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5411,73 +5838,85 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-500</v>
+        <v>-1300</v>
       </c>
       <c r="E89" s="3">
-        <v>300</v>
+        <v>-1300</v>
       </c>
       <c r="F89" s="3">
-        <v>-1600</v>
+        <v>-200</v>
       </c>
       <c r="G89" s="3">
-        <v>-3500</v>
+        <v>-200</v>
       </c>
       <c r="H89" s="3">
-        <v>6800</v>
+        <v>200</v>
       </c>
       <c r="I89" s="3">
+        <v>200</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-800</v>
+      </c>
+      <c r="K89" s="3">
         <v>6900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>5300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-3300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>1400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-4700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>1700</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R89" s="3">
         <v>-13200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-10200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>7300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-1700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>9300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-5800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>8500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5501,73 +5940,81 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="K91" s="3">
         <v>-2900</v>
       </c>
-      <c r="E91" s="3">
-        <v>-4300</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-4900</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-2000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-2400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-2400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-4000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-3800</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R91" s="3">
         <v>-2600</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-1800</v>
       </c>
       <c r="S91" s="3">
         <v>-1400</v>
       </c>
       <c r="T91" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="U91" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="V91" s="3">
         <v>-1100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-2400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-2400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5631,8 +6078,14 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5696,73 +6149,85 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="K94" s="3">
         <v>-2100</v>
       </c>
-      <c r="E94" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="G94" s="3">
+      <c r="L94" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="M94" s="3">
+        <v>3900</v>
+      </c>
+      <c r="N94" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="O94" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="P94" s="3">
         <v>-3600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R94" s="3">
+        <v>102500</v>
+      </c>
+      <c r="S94" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="T94" s="3">
         <v>-2100</v>
       </c>
-      <c r="I94" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="K94" s="3">
-        <v>3900</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P94" s="3">
-        <v>102500</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="R94" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-1700</v>
-      </c>
-      <c r="T94" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="U94" s="3">
-        <v>600</v>
       </c>
       <c r="V94" s="3">
         <v>-2400</v>
       </c>
       <c r="W94" s="3">
+        <v>600</v>
+      </c>
+      <c r="X94" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5786,31 +6251,33 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5851,8 +6318,14 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5916,8 +6389,14 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5981,8 +6460,14 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6046,96 +6531,108 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F100" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G100" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H100" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I100" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J100" s="3">
+        <v>2300</v>
+      </c>
+      <c r="K100" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="L100" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="M100" s="3">
+        <v>1200</v>
+      </c>
+      <c r="N100" s="3">
+        <v>-400</v>
+      </c>
+      <c r="O100" s="3">
+        <v>7900</v>
+      </c>
+      <c r="P100" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R100" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="S100" s="3">
+        <v>18800</v>
+      </c>
+      <c r="T100" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="U100" s="3">
+        <v>5100</v>
+      </c>
+      <c r="V100" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="W100" s="3">
+        <v>6400</v>
+      </c>
+      <c r="X100" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="Y100" s="3">
         <v>2400</v>
       </c>
-      <c r="E100" s="3">
-        <v>3400</v>
-      </c>
-      <c r="F100" s="3">
-        <v>4600</v>
-      </c>
-      <c r="G100" s="3">
-        <v>6800</v>
-      </c>
-      <c r="H100" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-4300</v>
-      </c>
-      <c r="K100" s="3">
-        <v>1200</v>
-      </c>
-      <c r="L100" s="3">
-        <v>-400</v>
-      </c>
-      <c r="M100" s="3">
-        <v>7900</v>
-      </c>
-      <c r="N100" s="3">
-        <v>1800</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P100" s="3">
-        <v>-72700</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>18800</v>
-      </c>
-      <c r="R100" s="3">
-        <v>-7300</v>
-      </c>
-      <c r="S100" s="3">
-        <v>5100</v>
-      </c>
-      <c r="T100" s="3">
-        <v>-8000</v>
-      </c>
-      <c r="U100" s="3">
-        <v>6400</v>
-      </c>
-      <c r="V100" s="3">
-        <v>-6500</v>
-      </c>
-      <c r="W100" s="3">
-        <v>2400</v>
-      </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -6153,92 +6650,104 @@
         <v>0</v>
       </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>-100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-100</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
         <v>-100</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
         <v>-200</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="E102" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="F102" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="G102" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="H102" s="3">
-        <v>-500</v>
+        <v>300</v>
       </c>
       <c r="I102" s="3">
+        <v>300</v>
+      </c>
+      <c r="J102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K102" s="3">
         <v>600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>1800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>300</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
-      <c r="O102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R102" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-1500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>1100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-1200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>1200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BGI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BGI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
   <si>
     <t>BGI</t>
   </si>
@@ -656,19 +656,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -683,304 +682,330 @@
     <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45655</v>
+      </c>
+      <c r="F7" s="2">
         <v>45563</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45471</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45381</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45290</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45192</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45010</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44464</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44282</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44100</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43918</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43736</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43554</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43372</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43190</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43001</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>42819</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>42637</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>42455</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>42273</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>42091</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>41909</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>34200</v>
+      </c>
+      <c r="E8" s="3">
+        <v>33900</v>
+      </c>
+      <c r="F8" s="3">
         <v>29700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>29300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>36000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>36900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>32600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>33200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>30100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>62300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>63300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>41500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>61100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>63200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>61800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>52700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>63500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>54000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>46900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>39900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>113000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>99700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>161900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>139700</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>21900</v>
+      </c>
+      <c r="E9" s="3">
+        <v>21700</v>
+      </c>
+      <c r="F9" s="3">
         <v>18100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>17800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>22100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>22700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>19200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>19600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>17800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>36600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>38700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>24900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>38000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>39100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>37600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>32500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>40500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>32300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>28400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>23500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>70000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>61300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>99500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>84300</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E10" s="3">
+        <v>12200</v>
+      </c>
+      <c r="F10" s="3">
         <v>11600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>11400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>13800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>14200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>13400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>13700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>12400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>25700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>24600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>16600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>23200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>24100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>24200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>20200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>23100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>21600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>18500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>16400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>43000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>38400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>62400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>55400</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1006,8 +1031,10 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1077,8 +1104,14 @@
       <c r="Y12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1148,16 +1181,22 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
+      <c r="D14" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1600</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>4</v>
@@ -1177,50 +1216,56 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3">
         <v>200</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>2900</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>500</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>500</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>5500</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1231,67 +1276,73 @@
         <v>1400</v>
       </c>
       <c r="F15" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G15" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H15" s="3">
         <v>1300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>1300</v>
-      </c>
-      <c r="H15" s="3">
-        <v>1100</v>
-      </c>
-      <c r="I15" s="3">
-        <v>1200</v>
       </c>
       <c r="J15" s="3">
         <v>1100</v>
       </c>
       <c r="K15" s="3">
+        <v>1200</v>
+      </c>
+      <c r="L15" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M15" s="3">
         <v>2400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>1900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>2100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>1800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>1800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>1500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>1500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>1300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>1400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>1100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>2000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>1900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>2900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1314,150 +1365,164 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>34400</v>
+      </c>
+      <c r="E17" s="3">
+        <v>34100</v>
+      </c>
+      <c r="F17" s="3">
         <v>29800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>29400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>35700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>36600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>32400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>33100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>31300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>60300</v>
-      </c>
-      <c r="L17" s="3">
-        <v>64400</v>
-      </c>
-      <c r="M17" s="3">
-        <v>42600</v>
       </c>
       <c r="N17" s="3">
         <v>64400</v>
       </c>
       <c r="O17" s="3">
+        <v>42600</v>
+      </c>
+      <c r="P17" s="3">
+        <v>64400</v>
+      </c>
+      <c r="Q17" s="3">
         <v>64700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>65700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>59200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>73000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>58800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>48100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>41300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>106000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>95200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>161900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>137000</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F18" s="3">
         <v>-100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>200</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="K18" s="3">
-        <v>2000</v>
       </c>
       <c r="L18" s="3">
         <v>-1100</v>
       </c>
       <c r="M18" s="3">
+        <v>2000</v>
+      </c>
+      <c r="N18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="O18" s="3">
         <v>-1000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-3200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-1600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-6500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-9500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-4900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-1300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-1400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>7000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>4500</v>
       </c>
-      <c r="X18" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1483,38 +1548,40 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F20" s="3">
         <v>-500</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-400</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-400</v>
       </c>
       <c r="G20" s="3">
         <v>-400</v>
       </c>
       <c r="H20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J20" s="3">
         <v>-500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-200</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
@@ -1554,221 +1621,245 @@
       <c r="Y20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E21" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F21" s="3">
         <v>1700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>1700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>1900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>2000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>1800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>1900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>4400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-2500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-1500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T21" s="3">
         <v>-8200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-3500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>7200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>6400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>2900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E22" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F22" s="3">
         <v>1500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>1500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>1800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>1800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>1200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>1300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>1000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>1200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>1200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>1000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>2400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>1800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>2100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>1400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>2000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>1200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>1000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>1500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>3600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>3900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>4600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="F23" s="3">
         <v>-1100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-1100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-1200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-1200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-2000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-2200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-2100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-5600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-3300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-7900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-11400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-6100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-2300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-2900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>3400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-4600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1793,11 +1884,11 @@
       <c r="J24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1838,8 +1929,14 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1909,150 +2006,168 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="F26" s="3">
         <v>-1100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-1100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-1200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-1200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-2000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-2200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-2100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-5600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-3300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-7900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-11400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-6100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-2300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-2900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>3400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-4600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-1100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-1200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-1200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-2000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-2200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-2100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-5600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-3300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-7900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-11400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-6100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-2300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-2900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>3400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-4600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2122,8 +2237,14 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2148,53 +2269,59 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>4</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="M29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>-300</v>
       </c>
-      <c r="O29" s="3">
+      <c r="Q29" s="3">
         <v>-100</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
         <v>-300</v>
       </c>
-      <c r="R29" s="3">
+      <c r="T29" s="3">
         <v>26700</v>
-      </c>
-      <c r="S29" s="3">
-        <v>1500</v>
-      </c>
-      <c r="T29" s="3">
-        <v>7600</v>
       </c>
       <c r="U29" s="3">
         <v>1500</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>7600</v>
+      </c>
+      <c r="W29" s="3">
+        <v>1500</v>
+      </c>
+      <c r="X29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2264,8 +2391,14 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2335,38 +2468,44 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>100</v>
+      </c>
+      <c r="E32" s="3">
+        <v>100</v>
+      </c>
+      <c r="F32" s="3">
         <v>500</v>
-      </c>
-      <c r="E32" s="3">
-        <v>400</v>
-      </c>
-      <c r="F32" s="3">
-        <v>400</v>
       </c>
       <c r="G32" s="3">
         <v>400</v>
       </c>
       <c r="H32" s="3">
+        <v>400</v>
+      </c>
+      <c r="I32" s="3">
+        <v>400</v>
+      </c>
+      <c r="J32" s="3">
         <v>500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>200</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
@@ -2406,79 +2545,91 @@
       <c r="Y32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="F33" s="3">
         <v>-1100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-1100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-1200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-1200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-2000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-2200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-2100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-6000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-3400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-8300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>15300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-4600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>5300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-1400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>3400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-4600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2548,155 +2699,173 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="F35" s="3">
         <v>-1100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-1100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-1200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-1200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-2000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-2200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-2100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-6000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-3400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-8300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>15300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-4600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>5300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-1400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>3400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-4600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45655</v>
+      </c>
+      <c r="F38" s="2">
         <v>45563</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45471</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45381</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45290</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45192</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45010</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44464</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44282</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44100</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43918</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43736</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43554</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43372</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43190</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43001</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>42819</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>42637</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>42455</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>42273</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>42091</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>41909</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2722,8 +2891,10 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2749,79 +2920,87 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1300</v>
+        <v>1100</v>
       </c>
       <c r="E41" s="3">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="F41" s="3">
         <v>1300</v>
       </c>
       <c r="G41" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H41" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I41" s="3">
         <v>1400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>2000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>2100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>1500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>2800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>1700</v>
-      </c>
-      <c r="W41" s="3">
-        <v>3000</v>
-      </c>
-      <c r="X41" s="3">
-        <v>2400</v>
       </c>
       <c r="Y41" s="3">
         <v>3000</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AA41" s="3">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2891,150 +3070,168 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E43" s="3">
+        <v>4600</v>
+      </c>
+      <c r="F43" s="3">
         <v>5200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>5100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>6200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>6400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>6700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>6800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>8300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>6000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>5400</v>
-      </c>
-      <c r="M43" s="3">
-        <v>4600</v>
-      </c>
-      <c r="N43" s="3">
-        <v>4400</v>
       </c>
       <c r="O43" s="3">
         <v>4600</v>
       </c>
       <c r="P43" s="3">
+        <v>4400</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>4600</v>
+      </c>
+      <c r="R43" s="3">
         <v>2700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>3100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>4800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>3700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>10300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>7300</v>
-      </c>
-      <c r="V43" s="3">
-        <v>7700</v>
-      </c>
-      <c r="W43" s="3">
-        <v>6800</v>
       </c>
       <c r="X43" s="3">
         <v>7700</v>
       </c>
       <c r="Y43" s="3">
+        <v>6800</v>
+      </c>
+      <c r="Z43" s="3">
+        <v>7700</v>
+      </c>
+      <c r="AA43" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>81400</v>
+      </c>
+      <c r="E44" s="3">
+        <v>80700</v>
+      </c>
+      <c r="F44" s="3">
         <v>78300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>77200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>73200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>75000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>68400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>69700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>64300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>65200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>72000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>73100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>74100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>75300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>68700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>67900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>66100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>59700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>100500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>103800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>102600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>101300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>135700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>150400</v>
       </c>
     </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3059,14 +3256,14 @@
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M45" s="3">
         <v>1600</v>
-      </c>
-      <c r="L45" s="3">
-        <v>1500</v>
-      </c>
-      <c r="M45" s="3">
-        <v>1500</v>
       </c>
       <c r="N45" s="3">
         <v>1500</v>
@@ -3075,161 +3272,173 @@
         <v>1500</v>
       </c>
       <c r="P45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="R45" s="3">
         <v>1600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>2600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>3800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>82200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>1700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>1600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>1300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>1400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>2200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>88500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>87700</v>
+      </c>
+      <c r="F46" s="3">
         <v>86800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>85600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>82900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>85000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>78600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>80100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>75400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>74700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>80200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>80900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>80300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>82500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>73900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>74500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>75600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>147700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>114000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>115600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>113300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>112500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>148000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>162600</v>
       </c>
     </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E47" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F47" s="3">
         <v>4000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>3900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>3000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>3100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>2500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>2500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>1400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>4200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>4200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>3400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>3300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>2900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>1000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>700</v>
       </c>
-      <c r="R47" s="3">
-        <v>0</v>
-      </c>
-      <c r="S47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T47" s="3" t="s">
-        <v>4</v>
+      <c r="T47" s="3">
+        <v>0</v>
       </c>
       <c r="U47" s="3" t="s">
         <v>4</v>
@@ -3240,156 +3449,174 @@
       <c r="W47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X47" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y47" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="X47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>42200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>41900</v>
+      </c>
+      <c r="F48" s="3">
         <v>45300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>44600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>57200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>58700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>58700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>59900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>59900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>60500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>60500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>62200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>65900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>68900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>22300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>18400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>15100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>11900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>17500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>21200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>21900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>22100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>28500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>31700</v>
       </c>
     </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F49" s="3">
         <v>6000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>5900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>5800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>6000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>5600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>5700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>5100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>4100</v>
-      </c>
-      <c r="L49" s="3">
-        <v>3600</v>
-      </c>
-      <c r="M49" s="3">
-        <v>3600</v>
       </c>
       <c r="N49" s="3">
         <v>3600</v>
       </c>
       <c r="O49" s="3">
+        <v>3600</v>
+      </c>
+      <c r="P49" s="3">
+        <v>3600</v>
+      </c>
+      <c r="Q49" s="3">
         <v>3200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>3300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>4500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>3000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>2800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3459,8 +3686,14 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3530,8 +3763,14 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3556,11 +3795,11 @@
       <c r="J52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -3584,25 +3823,31 @@
         <v>0</v>
       </c>
       <c r="T52" s="3">
+        <v>0</v>
+      </c>
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+      <c r="V52" s="3">
         <v>4200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>1600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>2700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3672,79 +3917,91 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>137200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>136000</v>
+      </c>
+      <c r="F54" s="3">
         <v>143100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>141000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>150100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>153900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>146500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>149400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>143200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>143500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>148500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>150100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>153100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>157600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>100500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>98200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>93800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>162300</v>
-      </c>
-      <c r="T54" s="3">
-        <v>136200</v>
-      </c>
-      <c r="U54" s="3">
-        <v>137700</v>
       </c>
       <c r="V54" s="3">
         <v>136200</v>
       </c>
       <c r="W54" s="3">
+        <v>137700</v>
+      </c>
+      <c r="X54" s="3">
+        <v>136200</v>
+      </c>
+      <c r="Y54" s="3">
         <v>136800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>180200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>198300</v>
       </c>
     </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3770,8 +4027,10 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3797,150 +4056,164 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>40700</v>
+      </c>
+      <c r="E57" s="3">
+        <v>40300</v>
+      </c>
+      <c r="F57" s="3">
         <v>33500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>33100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>31800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>32600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>28600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>29200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>27400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>25500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>28000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>26300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>35000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>29700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>25000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>20800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>20600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>19000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>35500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>35100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>34800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>31800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>44700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>46000</v>
       </c>
     </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>59800</v>
+      </c>
+      <c r="E58" s="3">
+        <v>59300</v>
+      </c>
+      <c r="F58" s="3">
         <v>62700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>61800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>54800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>56200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>52300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>53300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>48600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>37900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>41500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>45600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>42200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>44800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>36100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>36000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>31400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>46100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>55700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>56800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>50700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>58200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>69100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>79600</v>
       </c>
     </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3965,195 +4238,213 @@
       <c r="J59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M59" s="3">
         <v>12800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>12900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>9400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>7600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>8900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>7300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>6600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>5800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>79300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>6400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>5600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>6700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>5700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>8100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>104700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>103800</v>
+      </c>
+      <c r="F60" s="3">
         <v>100700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>99300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>91000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>93300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>85300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>87000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>81500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>76200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>82300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>81300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>84900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>83500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>68300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>63400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>57800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>144500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>97600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>97500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>92200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>95700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>121900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>133400</v>
       </c>
     </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>42000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>41600</v>
+      </c>
+      <c r="F61" s="3">
         <v>45300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>44700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>60900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>62400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>61500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>62700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>61900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>16500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>17000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>17200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>11800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>10700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>12100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>11100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>3800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>4400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>23200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>32400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>34700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>36200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>52000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>52000</v>
       </c>
     </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4164,67 +4455,73 @@
         <v>3100</v>
       </c>
       <c r="F62" s="3">
+        <v>3200</v>
+      </c>
+      <c r="G62" s="3">
+        <v>3100</v>
+      </c>
+      <c r="H62" s="3">
         <v>2000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>2000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>1300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>1300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>51100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>50200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>51200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>54000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>54700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>9700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>7000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>6900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>5900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>5600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>3500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>3600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>2700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>3400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4294,8 +4591,14 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4365,8 +4668,14 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4436,79 +4745,91 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>149800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>148500</v>
+      </c>
+      <c r="F66" s="3">
         <v>149200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>147100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>153900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>157800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>148100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>150900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>143700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>143800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>149500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>149600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>150700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>148900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>90100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>81500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>68500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>154800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>126400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>133400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>130400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>134600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>177400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>188700</v>
       </c>
     </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4534,8 +4855,10 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4605,8 +4928,14 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4676,8 +5005,14 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4747,8 +5082,14 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4818,79 +5159,91 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-96800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-96000</v>
+      </c>
+      <c r="F72" s="3">
         <v>-95300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-93900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-92700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-95000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-90900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-92600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-87900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-83700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-84400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-81400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-79100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-74600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-73900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-69500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-62200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-64900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-56300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-58700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-58700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-62100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-84300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-79700</v>
       </c>
     </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4960,8 +5313,14 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5031,8 +5390,14 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5102,79 +5467,91 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-12500</v>
+      </c>
+      <c r="F76" s="3">
         <v>-6100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-6000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-3800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>-3900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>-1500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>-1500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>-300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>-1000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>2500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>8600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>10300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>16700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>25300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>7600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>9700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>4300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>5700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>2200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>2800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>9600</v>
       </c>
     </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5244,155 +5621,173 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45655</v>
+      </c>
+      <c r="F80" s="2">
         <v>45563</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45471</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45381</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45290</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45192</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45010</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44464</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44282</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44100</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43918</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43736</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43554</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43372</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43190</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43001</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>42819</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>42637</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>42455</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>42273</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>42091</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>41909</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="F81" s="3">
         <v>-1100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-1100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-1200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-1200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-2000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-2200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-2100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-6000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-3400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-8300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>15300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-4600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>5300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-1400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>3400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-4600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5418,79 +5813,87 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E83" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F83" s="3">
         <v>1200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>1200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>1100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>1100</v>
-      </c>
-      <c r="H83" s="3">
-        <v>1000</v>
-      </c>
-      <c r="I83" s="3">
-        <v>1000</v>
       </c>
       <c r="J83" s="3">
         <v>1000</v>
       </c>
       <c r="K83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M83" s="3">
         <v>2400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>1900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>-1500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>1800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>1800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>1500</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T83" s="3">
         <v>1300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>1400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>1800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>2000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>2000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>1900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>3000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5560,8 +5963,14 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5631,8 +6040,14 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5702,8 +6117,14 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5773,8 +6194,14 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5844,79 +6271,91 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>500</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-1300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>6900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>5300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-3300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>1400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-4700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>1700</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T89" s="3">
         <v>-13200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-10200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>7300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-1700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>9300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-5800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>8500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5942,79 +6381,87 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F91" s="3">
         <v>-1800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-1700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-1000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-1400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-1400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-1300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-2900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-2000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-2400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-2400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-4000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T91" s="3">
         <v>-2600</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-1800</v>
       </c>
       <c r="U91" s="3">
         <v>-1400</v>
       </c>
       <c r="V91" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="W91" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="X91" s="3">
         <v>-1100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-2400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6084,8 +6531,14 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6155,79 +6608,91 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-1800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-1100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-1100</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-1600</v>
       </c>
       <c r="J94" s="3">
         <v>-1600</v>
       </c>
       <c r="K94" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="L94" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="M94" s="3">
         <v>-2100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-1500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>3900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-1800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-3000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T94" s="3">
         <v>102500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-2300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-2100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-1700</v>
-      </c>
-      <c r="V94" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="W94" s="3">
-        <v>600</v>
       </c>
       <c r="X94" s="3">
         <v>-2400</v>
       </c>
       <c r="Y94" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z94" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6253,8 +6718,10 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6279,11 +6746,11 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6324,8 +6791,14 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6395,8 +6868,14 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6466,8 +6945,14 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6537,79 +7022,91 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>200</v>
+      </c>
+      <c r="F100" s="3">
         <v>3100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>3100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>1200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>1300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>1700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>1700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>2300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-4100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-4300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>1200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>7900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>1800</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T100" s="3">
         <v>-72700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>18800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-7300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>5100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-8000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>6400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-6500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6634,11 +7131,11 @@
       <c r="J101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -6656,98 +7153,110 @@
         <v>0</v>
       </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
         <v>-100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-100</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
       <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
         <v>-100</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
         <v>-200</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>1800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>300</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T102" s="3">
         <v>-1300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-1500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>1100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-1200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>1200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BGI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BGI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="92">
   <si>
     <t>BGI</t>
   </si>
@@ -656,20 +656,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -684,328 +684,354 @@
     <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45927</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45835</v>
+      </c>
+      <c r="F7" s="2">
         <v>45745</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45655</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45563</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45471</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45381</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45290</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45192</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45010</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44464</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44282</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44100</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43918</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43736</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43554</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43372</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43190</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43001</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>42819</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>42637</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>42455</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>42273</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>42091</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>41909</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>33400</v>
+      </c>
+      <c r="E8" s="3">
+        <v>34100</v>
+      </c>
+      <c r="F8" s="3">
         <v>34200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>33900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>29700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>29300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>36000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>36900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>32600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>33200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>30100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>62300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>63300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>41500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>61100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>63200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>61800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>52700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>63500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>54000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>46900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>39900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>113000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>99700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>161900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>139700</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E9" s="3">
+        <v>20700</v>
+      </c>
+      <c r="F9" s="3">
         <v>21900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>21700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>18100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>17800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>22100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>22700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>19200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>19600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>17800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>36600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>38700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>24900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>38000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>39100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>37600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>32500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>40500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>32300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>28400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>23500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>70000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>61300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>99500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>84300</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>13400</v>
+      </c>
+      <c r="F10" s="3">
         <v>12300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>12200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>11600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>11400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>13800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>14200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>13400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>13700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>12400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>25700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>24600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>16600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>23200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>24100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>24200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>20200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>23100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>21600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>18500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>16400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>43000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>38400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>62400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>55400</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1033,8 +1059,10 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1110,8 +1138,14 @@
       <c r="AA12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1187,23 +1221,29 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
         <v>1600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>1600</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1222,55 +1262,61 @@
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R14" s="3">
         <v>200</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>2900</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>500</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>5500</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="E15" s="3">
         <v>1400</v>
@@ -1282,67 +1328,73 @@
         <v>1400</v>
       </c>
       <c r="H15" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I15" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J15" s="3">
         <v>1300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>1300</v>
-      </c>
-      <c r="J15" s="3">
-        <v>1100</v>
-      </c>
-      <c r="K15" s="3">
-        <v>1200</v>
       </c>
       <c r="L15" s="3">
         <v>1100</v>
       </c>
       <c r="M15" s="3">
+        <v>1200</v>
+      </c>
+      <c r="N15" s="3">
+        <v>1100</v>
+      </c>
+      <c r="O15" s="3">
         <v>2400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>1900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>2100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>1800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>1800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>1500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>1500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>1300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>1400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>1100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>2000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>1900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>2900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1367,162 +1419,176 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>33500</v>
+      </c>
+      <c r="E17" s="3">
+        <v>34200</v>
+      </c>
+      <c r="F17" s="3">
         <v>34400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>34100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>29800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>29400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>35700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>36600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>32400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>33100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>31300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>60300</v>
-      </c>
-      <c r="N17" s="3">
-        <v>64400</v>
-      </c>
-      <c r="O17" s="3">
-        <v>42600</v>
       </c>
       <c r="P17" s="3">
         <v>64400</v>
       </c>
       <c r="Q17" s="3">
+        <v>42600</v>
+      </c>
+      <c r="R17" s="3">
+        <v>64400</v>
+      </c>
+      <c r="S17" s="3">
         <v>64700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>65700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>59200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>73000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>58800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>48100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>41300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>106000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>95200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>161900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>137000</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F18" s="3">
         <v>-200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>200</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="M18" s="3">
-        <v>2000</v>
       </c>
       <c r="N18" s="3">
         <v>-1100</v>
       </c>
       <c r="O18" s="3">
+        <v>2000</v>
+      </c>
+      <c r="P18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-1000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-1600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-3900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-6500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-9500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-4900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-1300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-1400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>7000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>4500</v>
       </c>
-      <c r="Z18" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1550,44 +1616,46 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-500</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-400</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-400</v>
       </c>
       <c r="I20" s="3">
         <v>-400</v>
       </c>
       <c r="J20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L20" s="3">
         <v>-500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-200</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
@@ -1627,239 +1695,263 @@
       <c r="AA20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F21" s="3">
         <v>1200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>1200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>1700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>1700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>1900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>2000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>1800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>1900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>4400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-2500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-2400</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V21" s="3">
         <v>-8200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-3500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>7200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>6400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>2900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F22" s="3">
         <v>1600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>1600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>1500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>1500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>1800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>1800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>1200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>1300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>1000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>1200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>1200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>1000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>2400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>1800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>2100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>1400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>2000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>1200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>1000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>1500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>3600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>3900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>4600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F23" s="3">
         <v>-3400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-3400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-1100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-1100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-1200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-1200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-2000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-2200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-2100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-3300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-6000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-7900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-11400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-6100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-2300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-2900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>3400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-4600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1890,11 +1982,11 @@
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O24" s="3">
         <v>0</v>
@@ -1935,8 +2027,14 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2012,162 +2110,180 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F26" s="3">
         <v>-3400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-3400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-1100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-1100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-1200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-1200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-2000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-2200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-2100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-3300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-6000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-7900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-11400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-6100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-2300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-2900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>3400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-4600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F27" s="3">
         <v>-3400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-3400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-1100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-1100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-1200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-1200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-2000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-2200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-2100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-3300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-6000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-7900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-11400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-6100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-2300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-2900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>3400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-4600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2243,8 +2359,14 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2275,53 +2397,59 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>4</v>
+      <c r="M29" s="3">
+        <v>0</v>
       </c>
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>-300</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="S29" s="3">
         <v>-100</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
         <v>-300</v>
       </c>
-      <c r="T29" s="3">
+      <c r="V29" s="3">
         <v>26700</v>
-      </c>
-      <c r="U29" s="3">
-        <v>1500</v>
-      </c>
-      <c r="V29" s="3">
-        <v>7600</v>
       </c>
       <c r="W29" s="3">
         <v>1500</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>7600</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Z29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2397,8 +2525,14 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2474,44 +2608,50 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>500</v>
+      </c>
+      <c r="E32" s="3">
+        <v>500</v>
+      </c>
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>500</v>
-      </c>
-      <c r="G32" s="3">
-        <v>400</v>
-      </c>
-      <c r="H32" s="3">
-        <v>400</v>
       </c>
       <c r="I32" s="3">
         <v>400</v>
       </c>
       <c r="J32" s="3">
+        <v>400</v>
+      </c>
+      <c r="K32" s="3">
+        <v>400</v>
+      </c>
+      <c r="L32" s="3">
         <v>500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>200</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
@@ -2551,85 +2691,97 @@
       <c r="AA32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F33" s="3">
         <v>-3400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-3400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-1100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-1100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-1200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-1200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-2000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-2200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-2100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-3400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-5900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-8300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>15300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-4600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>5300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-1400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>3400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-4600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2705,167 +2857,185 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F35" s="3">
         <v>-3400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-3400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-1100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-1100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-1200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-1200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-2000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-2200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-2100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-3400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-5900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-8300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>15300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-4600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>5300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-1400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>3400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-4600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45927</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45835</v>
+      </c>
+      <c r="F38" s="2">
         <v>45745</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45655</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45563</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45471</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45381</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45290</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45192</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45010</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44464</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44282</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44100</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43918</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43736</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43554</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43372</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43190</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43001</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>42819</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>42637</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>42455</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>42273</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>42091</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>41909</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2893,8 +3063,10 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2922,85 +3094,93 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F41" s="3">
         <v>1100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1000</v>
-      </c>
-      <c r="F41" s="3">
-        <v>1300</v>
-      </c>
-      <c r="G41" s="3">
-        <v>1300</v>
       </c>
       <c r="H41" s="3">
         <v>1300</v>
       </c>
       <c r="I41" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J41" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K41" s="3">
         <v>1400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>2000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>1200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>2100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>1500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>2800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>1700</v>
-      </c>
-      <c r="Y41" s="3">
-        <v>3000</v>
-      </c>
-      <c r="Z41" s="3">
-        <v>2400</v>
       </c>
       <c r="AA41" s="3">
         <v>3000</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AC41" s="3">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3076,162 +3256,180 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E43" s="3">
+        <v>4200</v>
+      </c>
+      <c r="F43" s="3">
         <v>4600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>4600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>5200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>5100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>6200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>6400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>6700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>6800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>8300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>6000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>5400</v>
-      </c>
-      <c r="O43" s="3">
-        <v>4600</v>
-      </c>
-      <c r="P43" s="3">
-        <v>4400</v>
       </c>
       <c r="Q43" s="3">
         <v>4600</v>
       </c>
       <c r="R43" s="3">
+        <v>4400</v>
+      </c>
+      <c r="S43" s="3">
+        <v>4600</v>
+      </c>
+      <c r="T43" s="3">
         <v>2700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>3100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>4800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>3700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>10300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>7300</v>
-      </c>
-      <c r="X43" s="3">
-        <v>7700</v>
-      </c>
-      <c r="Y43" s="3">
-        <v>6800</v>
       </c>
       <c r="Z43" s="3">
         <v>7700</v>
       </c>
       <c r="AA43" s="3">
+        <v>6800</v>
+      </c>
+      <c r="AB43" s="3">
+        <v>7700</v>
+      </c>
+      <c r="AC43" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>88500</v>
+      </c>
+      <c r="E44" s="3">
+        <v>90400</v>
+      </c>
+      <c r="F44" s="3">
         <v>81400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>80700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>78300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>77200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>73200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>75000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>68400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>69700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>64300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>65200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>72000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>73100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>74100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>75300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>68700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>67900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>66100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>59700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>100500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>103800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>102600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>101300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>135700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>150400</v>
       </c>
     </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3262,14 +3460,14 @@
       <c r="L45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O45" s="3">
         <v>1600</v>
-      </c>
-      <c r="N45" s="3">
-        <v>1500</v>
-      </c>
-      <c r="O45" s="3">
-        <v>1500</v>
       </c>
       <c r="P45" s="3">
         <v>1500</v>
@@ -3278,173 +3476,185 @@
         <v>1500</v>
       </c>
       <c r="R45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="S45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="T45" s="3">
         <v>1600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>2600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>3800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>82200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>1700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>1600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>1300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>1400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>2200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>95600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>97600</v>
+      </c>
+      <c r="F46" s="3">
         <v>88500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>87700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>86800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>85600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>82900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>85000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>78600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>80100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>75400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>74700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>80200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>80900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>80300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>82500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>73900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>74500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>75600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>147700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>114000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>115600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>113300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>112500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>148000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>162600</v>
       </c>
     </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E47" s="3">
+        <v>4800</v>
+      </c>
+      <c r="F47" s="3">
         <v>3600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>3600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>4000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>3900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>3000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>3100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>2500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>2500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>1400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>4200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>4200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>3400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>3300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>2900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>1000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>700</v>
       </c>
-      <c r="T47" s="3">
-        <v>0</v>
-      </c>
-      <c r="U47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V47" s="3" t="s">
-        <v>4</v>
+      <c r="V47" s="3">
+        <v>0</v>
       </c>
       <c r="W47" s="3" t="s">
         <v>4</v>
@@ -3455,168 +3665,186 @@
       <c r="Y47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z47" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA47" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>49200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>50200</v>
+      </c>
+      <c r="F48" s="3">
         <v>42200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>41900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>45300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>44600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>57200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>58700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>58700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>59900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>59900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>60500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>60500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>62200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>65900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>68900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>22300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>18400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>15100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>11900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>17500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>21200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>21900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>22100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>28500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>31700</v>
       </c>
     </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E49" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F49" s="3">
         <v>2100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>2100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>6000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>5900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>5800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>6000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>5600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>5700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>5100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>4100</v>
-      </c>
-      <c r="N49" s="3">
-        <v>3600</v>
-      </c>
-      <c r="O49" s="3">
-        <v>3600</v>
       </c>
       <c r="P49" s="3">
         <v>3600</v>
       </c>
       <c r="Q49" s="3">
+        <v>3600</v>
+      </c>
+      <c r="R49" s="3">
+        <v>3600</v>
+      </c>
+      <c r="S49" s="3">
         <v>3200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>3300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>4500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>3000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>2800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3692,8 +3920,14 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3769,8 +4003,14 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3801,11 +4041,11 @@
       <c r="L52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
-      <c r="N52" s="3">
-        <v>0</v>
+      <c r="M52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O52" s="3">
         <v>0</v>
@@ -3829,25 +4069,31 @@
         <v>0</v>
       </c>
       <c r="V52" s="3">
+        <v>0</v>
+      </c>
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+      <c r="X52" s="3">
         <v>4200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>1600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>2700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3923,85 +4169,97 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>152900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>156100</v>
+      </c>
+      <c r="F54" s="3">
         <v>137200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>136000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>143100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>141000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>150100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>153900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>146500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>149400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>143200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>143500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>148500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>150100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>153100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>157600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>100500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>98200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>93800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>162300</v>
-      </c>
-      <c r="V54" s="3">
-        <v>136200</v>
-      </c>
-      <c r="W54" s="3">
-        <v>137700</v>
       </c>
       <c r="X54" s="3">
         <v>136200</v>
       </c>
       <c r="Y54" s="3">
+        <v>137700</v>
+      </c>
+      <c r="Z54" s="3">
+        <v>136200</v>
+      </c>
+      <c r="AA54" s="3">
         <v>136800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>180200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>198300</v>
       </c>
     </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4029,8 +4287,10 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4058,162 +4318,176 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>40800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>41700</v>
+      </c>
+      <c r="F57" s="3">
         <v>40700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>40300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>33500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>33100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>31800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>32600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>28600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>29200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>27400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>25500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>28000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>26300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>35000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>29700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>25000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>20800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>20600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>19000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>35500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>35100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>34800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>31800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>44700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>46000</v>
       </c>
     </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>62900</v>
+      </c>
+      <c r="E58" s="3">
+        <v>64200</v>
+      </c>
+      <c r="F58" s="3">
         <v>59800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>59300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>62700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>61800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>54800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>56200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>52300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>53300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>48600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>37900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>41500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>45600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>42200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>44800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>36100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>36000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>31400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>46100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>55700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>56800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>50700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>58200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>69100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>79600</v>
       </c>
     </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4244,215 +4518,233 @@
       <c r="L59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O59" s="3">
         <v>12800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>12900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>9400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>7600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>8900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>7300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>6600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>5800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>79300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>6400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>5600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>6700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>5700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>8100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>109100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>111400</v>
+      </c>
+      <c r="F60" s="3">
         <v>104700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>103800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>100700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>99300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>91000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>93300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>85300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>87000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>81500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>76200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>82300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>81300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>84900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>83500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>68300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>63400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>57800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>144500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>97600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>97500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>92200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>95700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>121900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>133400</v>
       </c>
     </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>56900</v>
+      </c>
+      <c r="E61" s="3">
+        <v>58100</v>
+      </c>
+      <c r="F61" s="3">
         <v>42000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>41600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>45300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>44700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>60900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>62400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>61500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>62700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>61900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>16500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>17000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>17200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>11800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>10700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>12100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>11100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>3800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>4400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>23200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>32400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>34700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>36200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>52000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>52000</v>
       </c>
     </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>3200</v>
+        <v>1700</v>
       </c>
       <c r="E62" s="3">
-        <v>3100</v>
+        <v>1700</v>
       </c>
       <c r="F62" s="3">
         <v>3200</v>
@@ -4461,67 +4753,73 @@
         <v>3100</v>
       </c>
       <c r="H62" s="3">
+        <v>3200</v>
+      </c>
+      <c r="I62" s="3">
+        <v>3100</v>
+      </c>
+      <c r="J62" s="3">
         <v>2000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>2000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>1300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>1300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>51100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>50200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>51200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>54000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>54700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>9700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>7000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>6900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>5900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>5600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>3500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>3600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>2700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>3400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4597,8 +4895,14 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4674,8 +4978,14 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4751,85 +5061,97 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>167600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>171100</v>
+      </c>
+      <c r="F66" s="3">
         <v>149800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>148500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>149200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>147100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>153900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>157800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>148100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>150900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>143700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>143800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>149500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>149600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>150700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>148900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>90100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>81500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>68500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>154800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>126400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>133400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>130400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>134600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>177400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>188700</v>
       </c>
     </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4857,8 +5179,10 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4934,8 +5258,14 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5011,8 +5341,14 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5088,8 +5424,14 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5165,85 +5507,97 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-101000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-103100</v>
+      </c>
+      <c r="F72" s="3">
         <v>-96800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-96000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-95300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-93900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-92700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-95000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-90900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-92600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-87900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-83700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-84400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-81400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-79100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-74600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-73900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-69500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-62200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-64900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-56300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-58700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-58700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-62100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-84300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-79700</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5319,8 +5673,14 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5396,8 +5756,14 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5473,85 +5839,97 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-14700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="F76" s="3">
         <v>-12600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-12500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-6100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>-6000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>-3800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>-3900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-1500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>-1500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>-400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>-300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>-1000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>2500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>8600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>10300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>16700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>25300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>7600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>9700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>4300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>5700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>2200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>2800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>9600</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5627,167 +6005,185 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45927</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45835</v>
+      </c>
+      <c r="F80" s="2">
         <v>45745</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45655</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45563</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45471</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45381</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45290</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45192</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45010</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44464</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44282</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44100</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43918</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43736</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43554</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43372</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43190</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43001</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>42819</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>42637</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>42455</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>42273</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>42091</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>41909</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F81" s="3">
         <v>-3400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-3400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-1100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-1100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-1200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-1200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-2000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-2200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-2100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-3400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-5900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-8300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>15300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-4600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>5300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-1400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>3400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-4600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5815,85 +6211,93 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E83" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F83" s="3">
         <v>1300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>1300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>1200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>1200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>1100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>1100</v>
-      </c>
-      <c r="J83" s="3">
-        <v>1000</v>
-      </c>
-      <c r="K83" s="3">
-        <v>1000</v>
       </c>
       <c r="L83" s="3">
         <v>1000</v>
       </c>
       <c r="M83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O83" s="3">
         <v>2400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>1900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>-1500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>1800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>1800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>1500</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V83" s="3">
         <v>1300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>1400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>1800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>2000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>2000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>1900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>3000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5969,8 +6373,14 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6046,8 +6456,14 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6123,8 +6539,14 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6200,8 +6622,14 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6277,85 +6705,97 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F89" s="3">
         <v>500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-1300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-1300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>6900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>5300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-3300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>1400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-4700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>1700</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V89" s="3">
         <v>-13200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-10200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>7300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-1700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>9300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-5800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>8500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6383,85 +6823,93 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F91" s="3">
         <v>-800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-1800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-1700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-1000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-1400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-1400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-1300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-2900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-2000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-2400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-4000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-3800</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V91" s="3">
         <v>-2600</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="V91" s="3">
-        <v>-1800</v>
       </c>
       <c r="W91" s="3">
         <v>-1400</v>
       </c>
       <c r="X91" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="Y91" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6537,8 +6985,14 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6614,85 +7068,97 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="F94" s="3">
         <v>-900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-1900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-1800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-1100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-1100</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-1600</v>
       </c>
       <c r="L94" s="3">
         <v>-1600</v>
       </c>
       <c r="M94" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="N94" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="O94" s="3">
         <v>-2100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-1500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>3900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-3000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-3600</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V94" s="3">
         <v>102500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-2300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-2100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-1700</v>
-      </c>
-      <c r="X94" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="Y94" s="3">
-        <v>600</v>
       </c>
       <c r="Z94" s="3">
         <v>-2400</v>
       </c>
       <c r="AA94" s="3">
+        <v>600</v>
+      </c>
+      <c r="AB94" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6720,8 +7186,10 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6752,11 +7220,11 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
@@ -6797,8 +7265,14 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6874,8 +7348,14 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6951,8 +7431,14 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7028,85 +7514,97 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E100" s="3">
+        <v>4900</v>
+      </c>
+      <c r="F100" s="3">
         <v>200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>3100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>3100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>1200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>1300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>1700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>1700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>2300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-4100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-4300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>1200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>7900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>1800</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V100" s="3">
         <v>-72700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>18800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-7300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>5100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>6400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-6500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7137,11 +7635,11 @@
       <c r="L101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
@@ -7159,104 +7657,116 @@
         <v>0</v>
       </c>
       <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
         <v>-100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-100</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
         <v>-100</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>-200</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>200</v>
+      </c>
+      <c r="F102" s="3">
         <v>-100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-100</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>1800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>300</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
-      <c r="S102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V102" s="3">
         <v>-1300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-1500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>1100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>1200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>600</v>
       </c>
     </row>
